--- a/importacao_87/Matriculas_87_relatorio.xlsx
+++ b/importacao_87/Matriculas_87_relatorio.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="140" customWidth="1" min="5" max="5"/>
@@ -477,7 +477,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Deixada de fora a pedido. A página é continuação do livro 2-AE fls. 04v: falta a descrição do imóvel e o proprietário.</t>
+          <t>Deixada de fora a pedido.</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NÃO IMPORTAR (falta conteúdo)</t>
+          <t>IMPORTAR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>A 3326 da consolidada (1) não é a matrícula 3326: os três atos têm os cabeçalhos "R-1-3324", "AV-1-3324" e "R-2-3324" e o texto diz "terreno objeto da matrícula nº 3.324". Imóvel (Rua Dr. Silva Jardim, 43,66 m²), proprietários, partes e datas são cópia exata da 3324 da mesma planilha (linha 2012), que já está no sistema. A DESCRICAO começa com "Falta". Nenhuma planilha tem o conteúdo verdadeiro da 3326, e nenhuma outra matrícula cita a 3326 (as 27 ocorrências de "3.326" são números de RG, de cadastro ou de carta de aforamento). Pista para a conferência: a Cópia 2-AE a 2-AZ tem dois registros diferentes com o número 3324. Um é o da Rua Dr. Silva Jardim (linhas 352/338/1205-1207), o que entrou no sistema. O outro é a casa da Rua Vergilina Pereira, nº 115 (linhas 638/609/2137-2140), aberta em 25/02/1986: Ednaldo Severino de Assis, depois Antônio Francisco Torres no R-3 de 04/03/1986, depois José Vidal Ferreira no R.4 de 03/12/2014. Esse segundo registro não aparece em nenhuma outra matrícula. Os textos dos dois dizem 3324, então só o livro pode dizer se um deles é a 3326. Falta transcrever do livro a 3326: abertura, proprietário, título anterior, descrição do imóvel e todos os atos. VERIFICADOR: a pista deve ser lida com cuidado. A Cópia 2-AE a 2-AZ transcreveu só as matrículas que faltavam no sistema (na faixa do livro 2-AM, 3321-3323, 3325 e 3327 já estavam no sistema e não aparecem na Cópia; 3324 e 3326 estavam na lista de faltantes). Ela traz dois registros com o número 3324 e nenhum com 3326, então é provável que um dos dois seja a 3326. Mas a cronologia aponta para o contrário do que parece: o da Rua Vergilina Pereira foi aberto em 25/02/1986 (R-1 em 25/02/1986, e o R.4 de 2014 tem o cabeçalho "R.4-3324") e o da Rua Dr. Silva Jardim em 26/02/1986. Como a 3328 foi aberta em 27/02/1986 e a numeração segue a data, a 3324 deveria ser a mais antiga (Vergilina Pereira) e a 3326 poderia ser a da Silva Jardim, que é justamente a que entrou no sistema como 3324. Os textos dos dois dizem 3324, então isso não pode ser decidido pelas planilhas: é preciso conferir no livro 2-AM qual imóvel está na 3324 e qual está na 3326 (e, se for o caso, corrigir também a 3324 já importada).</t>
+          <t>Conferido pelo usuário na imagem do livro: o conteúdo é mesmo da 3326, e o "3324" nos textos é erro de OCR. A sequência correta é R-1 (aforamento), AV-2 (construção) e R-3 (compra e venda). A data 06/02/1986 da AV-2, anterior ao R-1, é erro da fonte e foi mantida.</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H483"/>
+  <dimension ref="A1:H485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15252,96 +15252,72 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>DESCRICAO</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Transportado do Livro nº 2 AE, fls. 04 verso. suctivas, vencendo-se a primeira em 22/08/87 e a última em 22/07/90, sendo cada uma das seis primeiras de valor de CZ$ 4.470,00 (quatro mil, quatrocentos e setenta cruzados) e as 30 (trinta) subsequentes de valor correspondente, a contar da data do título juros 2.745% a.p./q. meses de p.m. Dejam em hipoteca, além do outro imóvel objeto da matrícula Santa Cruz do Capibaribe, 29 de julho de 1987. Eu, [Rúbrica] O Oficial do Registro</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>Transportado do Livro nº 2 AE, fls. 04 verso.</t>
-        </is>
-      </c>
+          <t>8154</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Depois da frase "Transportado do Livro nº 2 AE, fls. 04 verso." a DESCRICAO não descreve imóvel: é o final do texto do R-1 (hipoteca por cédula de crédito industrial), com as prestações ("vencendo-se a primeira em 22/08/87 e a última em 22/07/90 ... CZ$ 4.470,00") e o mesmo fecho do R-1 ("Dejam em hipoteca, além do outro imóvel objeto da matrícula Santa Cruz do Capibaribe, 29 de julho de 1987. Eu, [Rúbrica] O Oficial do Registro"). O "2.745% a.p./q." é o número da matrícula lido como taxa de juros. Esse trecho foi retirado e ficou só a referência à folha onde está a descrição. A descrição verdadeira não está em nenhuma planilha.</t>
+          <t>Parte "Renato Cordeiro de Arruda Júnior" (Adquirente, ID R-2) sem ato: a 3097 só tem R-1 e AV-2. É o adquirente do R-2 da matrícula 3091 (compra de Alvaro José de Lima, 29/02/1988); as duas linhas de "Renato Cordeiro de Arruda Júnior" vêm de outra matrícula. Na "Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx" havia dois registros com o número 3097: o do lote 18-B da quadra H do Loteamento Cruz Alta (Imobiliária Tapera -&gt; Alvaro José de Lima -&gt; Renato Cordeiro de Arruda Júnior -&gt; Givaldo Fernandes da Silva) e este, do lote 04 da quadra AB do Loteamento Bela Vista. O primeiro é a matrícula 3091: na "PLANILHA UNICA (1) (1).xlsx" (linhas 24-26) os mesmos atos têm os cabeçalhos "R.1 Mat 3091", "R.2 Mat 3091" e "R.3 Mat. 3.091", e a matrícula 27250 cita "R.3-Mats 3.088 e 3.091 ... em 26 de dezembro de 2006", que é a venda de Renato para Givaldo.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>DATA ABERTURA</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>31987.0</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>29/07/1987</t>
-        </is>
-      </c>
+          <t>8155</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Número de série de data do Excel (31987 = 29/07/1987), convertido para dd/mm/aaaa; é a mesma data do R-1 ("Santa Cruz do Capibaribe, 29 de julho de 1987").</t>
+          <t>Parte "Renato Cordeiro de Arruda Júnior" (Transmitente, ID R-3) sem ato: a 3097 não tem R-3. É o transmitente do R-3 da matrícula 3091 (venda a Givaldo Fernandes da Silva, 26/12/2006); as duas linhas de "Renato Cordeiro de Arruda Júnior" vêm de outra matrícula. Na "Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx" havia dois registros com o número 3097: o do lote 18-B da quadra H do Loteamento Cruz Alta (Imobiliária Tapera -&gt; Alvaro José de Lima -&gt; Renato Cordeiro de Arruda Júnior -&gt; Givaldo Fernandes da Silva) e este, do lote 04 da quadra AB do Loteamento Bela Vista. O primeiro é a matrícula 3091: na "PLANILHA UNICA (1) (1).xlsx" (linhas 24-26) os mesmos atos têm os cabeçalhos "R.1 Mat 3091", "R.2 Mat 3091" e "R.3 Mat. 3.091", e a matrícula 27250 cita "R.3-Mats 3.088 e 3.091 ... em 26 de dezembro de 2006", que é a venda de Renato para Givaldo.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -15351,118 +15327,82 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>ORDEM</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4053</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Formato: número 1.0 gravado como texto "1".</t>
+          <t>Ato "R-2-3238 CANCELADO" (COMPRA E VENDA (CANCELADO), 02/06/1993), REGISTRADO="N". O R-2 de 02/06/1993 (Paulo Ferreira da Silva e Elivoneide para Francisco Raimundo) foi cancelado no próprio livro: o texto termina com "NOTA: Em virtude de lapso, fica cancelado o registro nº R.2. MAT. 3.238 acima citado. Santa Cruz do Capibaribe, 02 de junho de 1993". O número R-2 foi usado de novo em 18/01/2000 para a venda a José Ademilson da Silva, e é esse o R-2 que vale: a matrícula 8950 (Cópia 2-CA a 2-CZ, linha 354) cita "R-2 - Mat. 3.238, às fls. 17, do livro nº 2-AL, em 18 de janeiro de 2000", e a numeração segue com AV.3, AV.4 e AV.5.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>NOTAS</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>(vazio)</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>NÃO CONSTA</t>
-        </is>
-      </c>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Formato: célula vazia vira "NÃO CONSTA".</t>
+          <t>Parte (transmitente Paulo Ferreira da Silva) do R-2 cancelado de 1993; ele continua como transmitente no R-2 de 18/01/2000 (linha 8306).</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>DATA ABERTURA</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>29/07/1987</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>NÃO CONSTA</t>
-        </is>
-      </c>
+          <t>8304</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr">
         <is>
-          <t>VERIFICADOR: 29/07/1987 (série 31987 da Cópia) é a data da hipoteca, não a da abertura. As matrículas vizinhas do mesmo livro 2-AE mostram que a 2745 foi aberta entre 31/10/1984 (2743) e 06/11/1984 (2746); a numeração é cronológica (2739-2742 em 26/10/1984, 2743 em 31/10/1984, 2746 em 06/11/1984, 2750 em 08/11/1984, 2751-2754 em 09/11/1984). A data exata não está em nenhuma planilha, por isso fica NÃO CONSTA em vez de uma data errada de 1987.</t>
+          <t>Parte (transmitente Elivoneide Lima de Souza Ferreira) do R-2 cancelado de 1993; ela continua como transmitente no R-2 de 18/01/2000 (linha 8307).</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -15477,7 +15417,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -15485,14 +15425,14 @@
       <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Parte "Renato Cordeiro de Arruda Júnior" (Adquirente, ID R-2) sem ato: a 3097 só tem R-1 e AV-2. É o adquirente do R-2 da matrícula 3091 (compra de Alvaro José de Lima, 29/02/1988); as duas linhas de "Renato Cordeiro de Arruda Júnior" vêm de outra matrícula. Na "Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx" havia dois registros com o número 3097: o do lote 18-B da quadra H do Loteamento Cruz Alta (Imobiliária Tapera -&gt; Alvaro José de Lima -&gt; Renato Cordeiro de Arruda Júnior -&gt; Givaldo Fernandes da Silva) e este, do lote 04 da quadra AB do Loteamento Bela Vista. O primeiro é a matrícula 3091: na "PLANILHA UNICA (1) (1).xlsx" (linhas 24-26) os mesmos atos têm os cabeçalhos "R.1 Mat 3091", "R.2 Mat 3091" e "R.3 Mat. 3.091", e a matrícula 27250 cita "R.3-Mats 3.088 e 3.091 ... em 26 de dezembro de 2006", que é a venda de Renato para Givaldo.</t>
+          <t>Parte (adquirente Francisco Raimundo) do R-2 cancelado de 1993; a venda a ele não teve efeito.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -15502,12 +15442,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
@@ -15515,19 +15455,19 @@
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Parte "Renato Cordeiro de Arruda Júnior" (Transmitente, ID R-3) sem ato: a 3097 não tem R-3. É o transmitente do R-3 da matrícula 3091 (venda a Givaldo Fernandes da Silva, 26/12/2006); as duas linhas de "Renato Cordeiro de Arruda Júnior" vêm de outra matrícula. Na "Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx" havia dois registros com o número 3097: o do lote 18-B da quadra H do Loteamento Cruz Alta (Imobiliária Tapera -&gt; Alvaro José de Lima -&gt; Renato Cordeiro de Arruda Júnior -&gt; Givaldo Fernandes da Silva) e este, do lote 04 da quadra AB do Loteamento Bela Vista. O primeiro é a matrícula 3091: na "PLANILHA UNICA (1) (1).xlsx" (linhas 24-26) os mesmos atos têm os cabeçalhos "R.1 Mat 3091", "R.2 Mat 3091" e "R.3 Mat. 3.091", e a matrícula 27250 cita "R.3-Mats 3.088 e 3.091 ... em 26 de dezembro de 2006", que é a venda de Renato para Givaldo.</t>
+          <t>Cadastro de Francisco Raimundo, que só aparecia no R-2 cancelado de 1993 e não é parte de nenhum outro ato.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -15537,172 +15477,244 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>4053</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
+          <t>3836</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>TEXTO</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>R-1-3324 TRANSMITENTE: [Prefeitura Municipal de Santa Cruz d</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>R-1-3326 TRANSMITENTE: [Prefeitura Municipal de Santa Cruz d</t>
+        </is>
+      </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Ato "R-2-3238 CANCELADO" (COMPRA E VENDA (CANCELADO), 02/06/1993), REGISTRADO="N". O R-2 de 02/06/1993 (Paulo Ferreira da Silva e Elivoneide para Francisco Raimundo) foi cancelado no próprio livro: o texto termina com "NOTA: Em virtude de lapso, fica cancelado o registro nº R.2. MAT. 3.238 acima citado. Santa Cruz do Capibaribe, 02 de junho de 1993". O número R-2 foi usado de novo em 18/01/2000 para a venda a José Ademilson da Silva, e é esse o R-2 que vale: a matrícula 8950 (Cópia 2-CA a 2-CZ, linha 354) cita "R-2 - Mat. 3.238, às fls. 17, do livro nº 2-AL, em 18 de janeiro de 2000", e a numeração segue com AV.3, AV.4 e AV.5.</t>
+          <t>confirmado pelo usuário na imagem: "3324" no texto é erro de OCR; o correto é 3326 (cabeçalho ajustado ao número do ato)</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>8303</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr"/>
+          <t>3837</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>ORDEM</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Parte (transmitente Paulo Ferreira da Silva) do R-2 cancelado de 1993; ele continua como transmitente no R-2 de 18/01/2000 (linha 8306).</t>
+          <t>confirmado pelo usuário na imagem: a sequência é R-1 (aforamento), AV-2 (construção), R-3 (compra e venda); a data da AV-2 (06/02/1986) é erro da fonte e foi mantida</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>8304</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
+          <t>3837</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>TEXTO</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>AV-1-3324 Certifico e dou fé, que conforme requerimento data</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>AV-2-3326 Certifico e dou fé, que conforme requerimento data</t>
+        </is>
+      </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Parte (transmitente Elivoneide Lima de Souza Ferreira) do R-2 cancelado de 1993; ela continua como transmitente no R-2 de 18/01/2000 (linha 8307).</t>
+          <t>confirmado pelo usuário na imagem: "3324" no texto é erro de OCR; o correto é 3326 (cabeçalho ajustado ao número do ato)</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>8305</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr"/>
+          <t>3838</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>ORDEM</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Parte (adquirente Francisco Raimundo) do R-2 cancelado de 1993; a venda a ele não teve efeito.</t>
+          <t>confirmado pelo usuário na imagem: a sequência é R-1 (aforamento), AV-2 (construção), R-3 (compra e venda); a data da AV-2 (06/02/1986) é erro da fonte e foi mantida</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>4309</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
+          <t>3838</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>TEXTO</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>R-2-3324 TRANSMITENTES: [Virginia Emilia Silva] e seu esposo</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>R-3-3326 TRANSMITENTES: [Virginia Emilia Silva] e seu esposo</t>
+        </is>
+      </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Cadastro de Francisco Raimundo, que só aparecia no R-2 cancelado de 1993 e não é parte de nenhum outro ato.</t>
+          <t>confirmado pelo usuário na imagem: "3324" no texto é erro de OCR; o correto é 3326 (cabeçalho ajustado ao número do ato)</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>4060</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
+          <t>7638</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>R-2</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>R-3</t>
+        </is>
+      </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Ato "AV-3-3.509" de 30/06/2006 (desmembramento em lotes "A" e "B") anulado no próprio livro: o texto termina com "Sem efeito em virtude de lapso." O número AV-3 foi usado de novo em 03/09/2007 para o remembramento com o imóvel nº 90, que fez o imóvel passar para a matrícula 11.003. Esse é o ato que vale: a matrícula 13285 diz que o imóvel do R.2-Mat. 3.509 está "atualmente matriculado e averbado sob o nº AV.1- Mat. 11.003, às fls. 57 ... em 03 de Setembro de 2007". Depois dele vem o R-4 (2009). Nenhuma parte estava ligada a este ato.</t>
+          <t>acompanha a renumeração da compra e venda para R-3</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -15717,39 +15729,39 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>PROPRIETARIO ATUAL</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R-2</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R-3</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Com o R-4 (venda a Pedro Ricardo da Silva, 1992), o R-5 e o R-6 acrescentados, a adquirente do R-1 deixou de ser proprietária. Os proprietários atuais passam a ser os do R-6 (Benigno Sebastião da Silva e Iracema Lopes da Silva), que já vêm marcados com "S" na Cópia.</t>
+          <t>acompanha a renumeração da compra e venda para R-3</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>linha acrescentada</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -15759,7 +15771,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2048</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
@@ -15767,7 +15779,7 @@
       <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Ato R-4 ("R-4-3.711...", 05/03/1992) da página de continuação da 3711 na Cópia, que faltava na base. A quebra de linha depois do cabeçalho virou espaço, como na base.</t>
+          <t>Ato "AV-3-3.509" de 30/06/2006 (desmembramento em lotes "A" e "B") anulado no próprio livro: o texto termina com "Sem efeito em virtude de lapso." O número AV-3 foi usado de novo em 03/09/2007 para o remembramento com o imóvel nº 90, que fez o imóvel passar para a matrícula 11.003. Esse é o ato que vale: a matrícula 13285 diz que o imóvel do R.2-Mat. 3.509 está "atualmente matriculado e averbado sob o nº AV.1- Mat. 11.003, às fls. 57 ... em 03 de Setembro de 2007". Depois dele vem o R-4 (2009). Nenhuma parte estava ligada a este ato.</t>
         </is>
       </c>
     </row>
@@ -15779,25 +15791,37 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>linha acrescentada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2049</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>PROPRIETARIO ATUAL</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Ato R-5 ("R-5-3.711...", 26/03/1999) da página de continuação da 3711 na Cópia, que faltava na base. A quebra de linha depois do cabeçalho virou espaço, como na base.</t>
+          <t>Com o R-4 (venda a Pedro Ricardo da Silva, 1992), o R-5 e o R-6 acrescentados, a adquirente do R-1 deixou de ser proprietária. Os proprietários atuais passam a ser os do R-6 (Benigno Sebastião da Silva e Iracema Lopes da Silva), que já vêm marcados com "S" na Cópia.</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15843,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2050</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2048</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
@@ -15827,7 +15851,7 @@
       <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Ato R-6 ("R-6-3.711...", 23/04/2001) da página de continuação da 3711 na Cópia, que faltava na base. A quebra de linha depois do cabeçalho virou espaço, como na base.</t>
+          <t>Ato R-4 ("R-4-3.711...", 05/03/1992) da página de continuação da 3711 na Cópia, que faltava na base. A quebra de linha depois do cabeçalho virou espaço, como na base.</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15873,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2051</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2049</t>
         </is>
       </c>
       <c r="E314" t="inlineStr"/>
@@ -15857,7 +15881,7 @@
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Ato R-7 ("R-7-3.711...", NÃO CONSTA) da página de continuação da 3711 na Cópia, que faltava na base. A quebra de linha depois do cabeçalho virou espaço, como na base.</t>
+          <t>Ato R-5 ("R-5-3.711...", 26/03/1999) da página de continuação da 3711 na Cópia, que faltava na base. A quebra de linha depois do cabeçalho virou espaço, como na base.</t>
         </is>
       </c>
     </row>
@@ -15874,12 +15898,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4248</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2050</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
@@ -15887,7 +15911,7 @@
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Parte Adquirente "Pedro Ricardo da Silva" do R-4-3.711, ato acrescentado da mesma página da Cópia.</t>
+          <t>Ato R-6 ("R-6-3.711...", 23/04/2001) da página de continuação da 3711 na Cópia, que faltava na base. A quebra de linha depois do cabeçalho virou espaço, como na base.</t>
         </is>
       </c>
     </row>
@@ -15904,12 +15928,12 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4249</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2051</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
@@ -15917,7 +15941,7 @@
       <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Parte Transmitente "Pedro Ricardo da Silva" do R-5-3.711, ato acrescentado da mesma página da Cópia.</t>
+          <t>Ato R-7 ("R-7-3.711...", NÃO CONSTA) da página de continuação da 3711 na Cópia, que faltava na base. A quebra de linha depois do cabeçalho virou espaço, como na base.</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15963,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4250</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4248</t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
@@ -15947,7 +15971,7 @@
       <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Parte Transmitente "Lucilita de Oliveira Silva" do R-5-3.711, ato acrescentado da mesma página da Cópia.</t>
+          <t>Parte Adquirente "Pedro Ricardo da Silva" do R-4-3.711, ato acrescentado da mesma página da Cópia.</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15993,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4251</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4249</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -15977,7 +16001,7 @@
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Parte Adquirente "Josefa Jaksilene Menezes de Barros" do R-5-3.711, ato acrescentado da mesma página da Cópia.</t>
+          <t>Parte Transmitente "Pedro Ricardo da Silva" do R-5-3.711, ato acrescentado da mesma página da Cópia.</t>
         </is>
       </c>
     </row>
@@ -15999,7 +16023,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4252</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4250</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
@@ -16007,7 +16031,7 @@
       <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Parte Transmitente "Josya Jaksiline Menezes de Barros" do R-6-3.711, ato acrescentado da mesma página da Cópia.</t>
+          <t>Parte Transmitente "Lucilita de Oliveira Silva" do R-5-3.711, ato acrescentado da mesma página da Cópia.</t>
         </is>
       </c>
     </row>
@@ -16029,7 +16053,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4253</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4251</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
@@ -16037,7 +16061,7 @@
       <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Parte Adquirente "Benigno Sebastião da Silva" do R-6-3.711, ato acrescentado da mesma página da Cópia.</t>
+          <t>Parte Adquirente "Josefa Jaksilene Menezes de Barros" do R-5-3.711, ato acrescentado da mesma página da Cópia.</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16083,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4254</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4252</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
@@ -16067,7 +16091,7 @@
       <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Parte Adquirente "Iracema Lopes da Silva" do R-6-3.711, ato acrescentado da mesma página da Cópia.</t>
+          <t>Parte Transmitente "Josya Jaksiline Menezes de Barros" do R-6-3.711, ato acrescentado da mesma página da Cópia.</t>
         </is>
       </c>
     </row>
@@ -16084,12 +16108,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2083</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4253</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -16097,7 +16121,7 @@
       <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Cadastro de "Maria Francisca das Graças", parte dos atos R-4 a R-6 acrescentados.</t>
+          <t>Parte Adquirente "Benigno Sebastião da Silva" do R-6-3.711, ato acrescentado da mesma página da Cópia.</t>
         </is>
       </c>
     </row>
@@ -16114,12 +16138,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2084</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 4254</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -16127,7 +16151,7 @@
       <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Cadastro de "Pedro Ricardo da Silva", parte dos atos R-4 a R-6 acrescentados.</t>
+          <t>Parte Adquirente "Iracema Lopes da Silva" do R-6-3.711, ato acrescentado da mesma página da Cópia.</t>
         </is>
       </c>
     </row>
@@ -16149,7 +16173,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2085</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2083</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
@@ -16157,7 +16181,7 @@
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Cadastro de "Lucilita de Oliveira Silva", parte dos atos R-4 a R-6 acrescentados.</t>
+          <t>Cadastro de "Maria Francisca das Graças", parte dos atos R-4 a R-6 acrescentados.</t>
         </is>
       </c>
     </row>
@@ -16179,7 +16203,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2086</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2084</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
@@ -16187,7 +16211,7 @@
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Cadastro de "Josefa Jaksilene Menezes de Barros", parte dos atos R-4 a R-6 acrescentados.</t>
+          <t>Cadastro de "Pedro Ricardo da Silva", parte dos atos R-4 a R-6 acrescentados.</t>
         </is>
       </c>
     </row>
@@ -16209,7 +16233,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2087</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2085</t>
         </is>
       </c>
       <c r="E326" t="inlineStr"/>
@@ -16217,7 +16241,7 @@
       <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Cadastro de "Josya Jaksiline Menezes de Barros", parte dos atos R-4 a R-6 acrescentados.</t>
+          <t>Cadastro de "Lucilita de Oliveira Silva", parte dos atos R-4 a R-6 acrescentados.</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16263,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2088</t>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2086</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
@@ -16247,91 +16271,67 @@
       <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Cadastro de "Benigno Sebastião da Silva", parte dos atos R-4 a R-6 acrescentados.</t>
+          <t>Cadastro de "Josefa Jaksilene Menezes de Barros", parte dos atos R-4 a R-6 acrescentados.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha acrescentada</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>1797</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>PROTOCOLO</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>423/2002</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>NÃO CONSTA</t>
-        </is>
-      </c>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2087</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr">
         <is>
-          <t>VERIFICADOR: "423/2002" é o número do Ofício judicial citado no texto ("Ofício nº 423/2002. Em, 22 de Julho de 2002"), não um protocolo do cartório, e o importador só aceita "NÃO CONSTA" ou número de até 9 dígitos (regra R3). Esta era a causa da rejeição. O verificador desfez a retirada do R-7 e do R-8 que o resolvedor tinha feito, porque os dois atos são do imóvel desta matrícula: (1) o ofício grava "Uma casa situada na Rua Cabo Otávio Aragão, nº 194", que é o prédio averbado na AV-2-4.587; (2) o cabeçalho "4.584" não pode ser da 4584 real (salão da Av. 29 de Dezembro, 408), cuja AV-5 é de 17/04/2009 e cujo R-6 é de 31/03/2014, com venda pelo Espólio de Severino João Bezerra, o que é incompatível com um R-7 de 2002 e uma arrematação de 2005 por outra pessoa; (3) na "Cópia de PLANILHA SANTA 2-BA a 2-BZ" a folha "4584" desses atos diz "Transportado do Livro Nº 2-BB - Fls 01 V", e o ofício situa o registro da casa às "fls. 01 verso, do livro nº 2-BB"; (4) o imóvel vizinho (Rua São Miguel, 131, matrícula 4590), alvo do mesmo ofício, recebeu sua própria arrematação na folha "4.590". A base verificada pelo usuário (Matrículas faltantes) já punha esses atos na 4587.</t>
+          <t>Cadastro de "Josya Jaksiline Menezes de Barros", parte dos atos R-4 a R-6 acrescentados.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha acrescentada</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>3740</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>PROTOCOLO</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>423/2002</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>NÃO CONSTA</t>
-        </is>
-      </c>
+          <t>Cópia de PLANILHA SANTA 2-AE a 2-AZ.xlsx linha 2088</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr">
         <is>
-          <t>VERIFICADOR: mesmo protocolo inválido "423/2002" (número do Ofício) na parte do R-7; ajustado para ficar igual ao ato.</t>
+          <t>Cadastro de "Benigno Sebastião da Silva", parte dos atos R-4 a R-6 acrescentados.</t>
         </is>
       </c>
     </row>
@@ -16348,12 +16348,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -16373,49 +16373,61 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>VERIFICADOR: mesmo protocolo inválido "423/2002" (número do Ofício) na parte do R-7; ajustado para ficar igual ao ato.</t>
+          <t>VERIFICADOR: "423/2002" é o número do Ofício judicial citado no texto ("Ofício nº 423/2002. Em, 22 de Julho de 2002"), não um protocolo do cartório, e o importador só aceita "NÃO CONSTA" ou número de até 9 dígitos (regra R3). Esta era a causa da rejeição. O verificador desfez a retirada do R-7 e do R-8 que o resolvedor tinha feito, porque os dois atos são do imóvel desta matrícula: (1) o ofício grava "Uma casa situada na Rua Cabo Otávio Aragão, nº 194", que é o prédio averbado na AV-2-4.587; (2) o cabeçalho "4.584" não pode ser da 4584 real (salão da Av. 29 de Dezembro, 408), cuja AV-5 é de 17/04/2009 e cujo R-6 é de 31/03/2014, com venda pelo Espólio de Severino João Bezerra, o que é incompatível com um R-7 de 2002 e uma arrematação de 2005 por outra pessoa; (3) na "Cópia de PLANILHA SANTA 2-BA a 2-BZ" a folha "4584" desses atos diz "Transportado do Livro Nº 2-BB - Fls 01 V", e o ofício situa o registro da casa às "fls. 01 verso, do livro nº 2-BB"; (4) o imóvel vizinho (Rua São Miguel, 131, matrícula 4590), alvo do mesmo ofício, recebeu sua própria arrematação na folha "4.590". A base verificada pelo usuário (Matrículas faltantes) já punha esses atos na 4587.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>4124</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
-      <c r="G331" t="inlineStr"/>
+          <t>3740</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>PROTOCOLO</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>423/2002</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>NÃO CONSTA</t>
+        </is>
+      </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Ato "R-3-4732" é um lançamento anulado no próprio livro: o texto termina em "ADQUIRENTE: Sem efeito. Santa Cruz do Cap. 20/01/99", sem adquirente, título ou valor. A transmissão que ele começava (Amaro Honorato da Silva e Vera Lúcia da Silva) foi refeita no R-4-4732 da mesma data, e o número 3 da sequência única R/AV ficou com a AV-3-4732 (construção, protocolo 11.404): R-1, R-2, AV-3, R-4, AV-5 fecham a sequência 1-5 sem lacunas.</t>
+          <t>VERIFICADOR: mesmo protocolo inválido "423/2002" (número do Ofício) na parte do R-7; ajustado para ficar igual ao ato.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -16425,15 +16437,27 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>8429</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
+          <t>3741</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>PROTOCOLO</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>423/2002</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>NÃO CONSTA</t>
+        </is>
+      </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Parte (transmitente Amaro Honorato da Silva) do R-3 "sem efeito" removido; a mesma pessoa continua como transmitente no R-4.</t>
+          <t>VERIFICADOR: mesmo protocolo inválido "423/2002" (número do Ofício) na parte do R-7; ajustado para ficar igual ao ato.</t>
         </is>
       </c>
     </row>
@@ -16450,12 +16474,12 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
@@ -16463,91 +16487,67 @@
       <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Parte (transmitente Vera Lúcia da Silva) do R-3 "sem efeito" removido; a mesma pessoa continua como transmitente no R-4.</t>
+          <t>Ato "R-3-4732" é um lançamento anulado no próprio livro: o texto termina em "ADQUIRENTE: Sem efeito. Santa Cruz do Cap. 20/01/99", sem adquirente, título ou valor. A transmissão que ele começava (Amaro Honorato da Silva e Vera Lúcia da Silva) foi refeita no R-4-4732 da mesma data, e o número 3 da sequência única R/AV ficou com a AV-3-4732 (construção, protocolo 11.404): R-1, R-2, AV-3, R-4, AV-5 fecham a sequência 1-5 sem lacunas.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>ORDEM</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>8429</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Averbação de construção (certidão municipal) de 25/01/1991, lançada no mesmo dia do R-1 (aforamento). Como R e AV dividem uma única numeração, "AV-1" colide com o R-1; pela ordem cronológica ela é o 2º ato.</t>
+          <t>Parte (transmitente Amaro Honorato da Silva) do R-3 "sem efeito" removido; a mesma pessoa continua como transmitente no R-4.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>3954</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>ORDEM</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>8430</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Partilha de 31/01/1991 (dissolução de sociedade de fato, imóvel passa a Jozilda Monteiro da Silva), posterior à averbação de construção de 25/01/1991; com a correção anterior passa a ser o 3º ato da sequência única.</t>
+          <t>Parte (transmitente Vera Lúcia da Silva) do R-3 "sem efeito" removido; a mesma pessoa continua como transmitente no R-4.</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -16579,24 +16579,24 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Averbação "Em tempo" de 31/01/1991 que completa a qualificação da adquirente da partilha; vem logo depois dela, logo é o 4º ato da sequência única.</t>
+          <t>Averbação de construção (certidão municipal) de 25/01/1991, lançada no mesmo dia do R-1 (aforamento). Como R e AV dividem uma única numeração, "AV-1" colide com o R-1; pela ordem cronológica ela é o 2º ato.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -16606,39 +16606,39 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>AREA TOTAL</t>
+          <t>ORDEM</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>360,00</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>130,36</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>VERIFICADOR: o T. URBANO da base (Rua Pedro Teodoro Aragão, 12 x 30 m, 360 m², vizinhos José Goza de Souza, Marciano Pereira de Ramos e Edmilson Glicério da Silva) não é o imóvel da 5092 e não aparece em nenhum texto desta matrícula. A abertura da própria matrícula, na NOTA que precede o "R.1. MAT. Nº 5.092" (de onde a base já tirou PROPRIETARIOS e MATRICULA ANTERIOR), descreve o terreno da Rua Francisco Antonio Aragão, s/nº, 06,00 x 04,20 x 25,80 x 21,40 m, 130,36 m²; a AV-2 ("terreno objeto da matrícula nº 5.092 ... Francisco Antonio Aragão, nº 375") e o T. URBANO da "Cópia de PLANILHA SANTA 2-BA a 2-BZ" (linha 549) confirmam. O T. URBANO de Pedro Teodoro Aragão vinha junto com o R-1 copiado (linha 75: TRANSMISSÃO a José Ramos de Moura, 04/06/1992) que o resolvedor já retirou por não ter texto na 5092.</t>
+          <t>Partilha de 31/01/1991 (dissolução de sociedade de fato, imóvel passa a Jozilda Monteiro da Silva), posterior à averbação de construção de 25/01/1991; com a correção anterior passa a ser o 3º ato da sequência única.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -16648,32 +16648,32 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>LOGRADOURO</t>
+          <t>ORDEM</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Rua Pedro Teodoro Aragão</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Rua Francisco Antonio Aragão</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>VERIFICADOR: o T. URBANO da base (Rua Pedro Teodoro Aragão, 12 x 30 m, 360 m², vizinhos José Goza de Souza, Marciano Pereira de Ramos e Edmilson Glicério da Silva) não é o imóvel da 5092 e não aparece em nenhum texto desta matrícula. A abertura da própria matrícula, na NOTA que precede o "R.1. MAT. Nº 5.092" (de onde a base já tirou PROPRIETARIOS e MATRICULA ANTERIOR), descreve o terreno da Rua Francisco Antonio Aragão, s/nº, 06,00 x 04,20 x 25,80 x 21,40 m, 130,36 m²; a AV-2 ("terreno objeto da matrícula nº 5.092 ... Francisco Antonio Aragão, nº 375") e o T. URBANO da "Cópia de PLANILHA SANTA 2-BA a 2-BZ" (linha 549) confirmam. O T. URBANO de Pedro Teodoro Aragão vinha junto com o R-1 copiado (linha 75: TRANSMISSÃO a José Ramos de Moura, 04/06/1992) que o resolvedor já retirou por não ter texto na 5092.</t>
+          <t>Averbação "Em tempo" de 31/01/1991 que completa a qualificação da adquirente da partilha; vem logo depois dela, logo é o 4º ato da sequência única.</t>
         </is>
       </c>
     </row>
@@ -16700,17 +16700,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>DESCRICAO</t>
+          <t>AREA TOTAL</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Um terreno do patrimônio do município, localizado na Rua Pedro Teodoro Aragão, s/nº, nesta cidade, medindo 12,00 metros de frente, 12,00 metros de fundos, 30,00 metros na lateral direita e 30,00 metros na lateral esquerda, com área total de: 360,00 m2, para fins residencial, limitando-se na parte da frente com o leito da Rua Pedro Teodoro Aragão, na parte de trás com [José Goza de Souza] (imóvel nº 152 da Rua Pe. Claudio Abílio Aragão), do lado direito com [Marciano Pereira de Ramos] (imóvel nº 163) e do lado esquerdo com [Edmilson Glicério da Silva] (imóvel nº 188)</t>
+          <t>360,00</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Um terreno do patrimônio do município, localizado à Rua Francisco Antonio Aragão, s/nº, nesta cidade, medindo 06,00 metros de frente, 04,20 metros de fundos, 25,80 metros na lateral direita e 21,40 metros na lateral esquerda com área total de 130,36 m2, para fins residenciais, limitando-se na parte da frente com o leito da Rua Francisco Antonio Aragão, na parte de trás com o leito da Rua Padre José Anchieta, do lado direito com [Ana Maria Alves de Araújo] (imóvel 371) e do lado esquerdo com [Inacio Graca da Silva] (imóvel nº 379).</t>
+          <t>130,36</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>T. URBANO</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>DATA ABERTURA</t>
+          <t>LOGRADOURO</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>04/06/1992</t>
+          <t>Rua Pedro Teodoro Aragão</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>08/06/1992</t>
+          <t>Rua Francisco Antonio Aragão</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>VERIFICADOR: a abertura (NOTA) e o R-1 formam um só lançamento, que termina em "Santa Cruz do Capibaribe, 08 de junho de 1992"; a AV-2 também é de 08/06/1992 e a "Cópia de PLANILHA SANTA 2-BA a 2-BZ" (linha 559) traz DATA ABERTURA 33763 = 08/06/1992. A data 04/06/1992 é a do R-1 copiado (linha 75, José Ramos de Moura) que foi retirado.</t>
+          <t>VERIFICADOR: o T. URBANO da base (Rua Pedro Teodoro Aragão, 12 x 30 m, 360 m², vizinhos José Goza de Souza, Marciano Pereira de Ramos e Edmilson Glicério da Silva) não é o imóvel da 5092 e não aparece em nenhum texto desta matrícula. A abertura da própria matrícula, na NOTA que precede o "R.1. MAT. Nº 5.092" (de onde a base já tirou PROPRIETARIOS e MATRICULA ANTERIOR), descreve o terreno da Rua Francisco Antonio Aragão, s/nº, 06,00 x 04,20 x 25,80 x 21,40 m, 130,36 m²; a AV-2 ("terreno objeto da matrícula nº 5.092 ... Francisco Antonio Aragão, nº 375") e o T. URBANO da "Cópia de PLANILHA SANTA 2-BA a 2-BZ" (linha 549) confirmam. O T. URBANO de Pedro Teodoro Aragão vinha junto com o R-1 copiado (linha 75: TRANSMISSÃO a José Ramos de Moura, 04/06/1992) que o resolvedor já retirou por não ter texto na 5092.</t>
         </is>
       </c>
     </row>
@@ -16769,25 +16769,37 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>T. URBANO</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
-      <c r="G341" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>DESCRICAO</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Um terreno do patrimônio do município, localizado na Rua Pedro Teodoro Aragão, s/nº, nesta cidade, medindo 12,00 metros de frente, 12,00 metros de fundos, 30,00 metros na lateral direita e 30,00 metros na lateral esquerda, com área total de: 360,00 m2, para fins residencial, limitando-se na parte da frente com o leito da Rua Pedro Teodoro Aragão, na parte de trás com [José Goza de Souza] (imóvel nº 152 da Rua Pe. Claudio Abílio Aragão), do lado direito com [Marciano Pereira de Ramos] (imóvel nº 163) e do lado esquerdo com [Edmilson Glicério da Silva] (imóvel nº 188)</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Um terreno do patrimônio do município, localizado à Rua Francisco Antonio Aragão, s/nº, nesta cidade, medindo 06,00 metros de frente, 04,20 metros de fundos, 25,80 metros na lateral direita e 21,40 metros na lateral esquerda com área total de 130,36 m2, para fins residenciais, limitando-se na parte da frente com o leito da Rua Francisco Antonio Aragão, na parte de trás com o leito da Rua Padre José Anchieta, do lado direito com [Ana Maria Alves de Araújo] (imóvel 371) e do lado esquerdo com [Inacio Graca da Silva] (imóvel nº 379).</t>
+        </is>
+      </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Cópia do R-1: o TEXTO é igual ao da linha 76 (só muda "residencial"/"residenciais"). Os dois trazem a NOTA com a descrição do terreno da Rua Francisco Antonio Aragão e o "R.1. MAT. Nº 5.092", aforamento da Prefeitura a Maria Jozé da Silva, datado de 08/06/1992. Fica a linha 76 (ATO AFORAMENTO, DATA 08/06/1992, igual à data do texto). Esta linha (ATO TRANSMISSÃO, DATA 04/06/1992) não tem texto próprio.</t>
+          <t>VERIFICADOR: o T. URBANO da base (Rua Pedro Teodoro Aragão, 12 x 30 m, 360 m², vizinhos José Goza de Souza, Marciano Pereira de Ramos e Edmilson Glicério da Silva) não é o imóvel da 5092 e não aparece em nenhum texto desta matrícula. A abertura da própria matrícula, na NOTA que precede o "R.1. MAT. Nº 5.092" (de onde a base já tirou PROPRIETARIOS e MATRICULA ANTERIOR), descreve o terreno da Rua Francisco Antonio Aragão, s/nº, 06,00 x 04,20 x 25,80 x 21,40 m, 130,36 m²; a AV-2 ("terreno objeto da matrícula nº 5.092 ... Francisco Antonio Aragão, nº 375") e o T. URBANO da "Cópia de PLANILHA SANTA 2-BA a 2-BZ" (linha 549) confirmam. O T. URBANO de Pedro Teodoro Aragão vinha junto com o R-1 copiado (linha 75: TRANSMISSÃO a José Ramos de Moura, 04/06/1992) que o resolvedor já retirou por não ter texto na 5092.</t>
         </is>
       </c>
     </row>
@@ -16799,25 +16811,37 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRÍCULA</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>DATA ABERTURA</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>04/06/1992</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>08/06/1992</t>
+        </is>
+      </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Transmitente Prefeitura Municipal da cópia do R-1 removida; a mesma parte continua na linha 154, ligada ao R-1 que fica.</t>
+          <t>VERIFICADOR: a abertura (NOTA) e o R-1 formam um só lançamento, que termina em "Santa Cruz do Capibaribe, 08 de junho de 1992"; a AV-2 também é de 08/06/1992 e a "Cópia de PLANILHA SANTA 2-BA a 2-BZ" (linha 559) traz DATA ABERTURA 33763 = 08/06/1992. A data 04/06/1992 é a do R-1 copiado (linha 75, José Ramos de Moura) que foi retirado.</t>
         </is>
       </c>
     </row>
@@ -16834,12 +16858,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
@@ -16847,91 +16871,67 @@
       <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Adquirente "José Ramos de Moura" ligado só à cópia do R-1 removida. Nenhum texto desta matrícula, em nenhuma versão, cita esse nome, e o R-1 cujo texto existe ("R.1. MAT. Nº 5.092") tem como adquirente Maria Jozé da Silva.</t>
+          <t>Cópia do R-1: o TEXTO é igual ao da linha 76 (só muda "residencial"/"residenciais"). Os dois trazem a NOTA com a descrição do terreno da Rua Francisco Antonio Aragão e o "R.1. MAT. Nº 5.092", aforamento da Prefeitura a Maria Jozé da Silva, datado de 08/06/1992. Fica a linha 76 (ATO AFORAMENTO, DATA 08/06/1992, igual à data do texto). Esta linha (ATO TRANSMISSÃO, DATA 04/06/1992) não tem texto próprio.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>DATA ABERTURA</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>08 de fevereiro de 1994</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>08/02/1994</t>
-        </is>
-      </c>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr"/>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Data escrita por extenso ("08 de fevereiro de 1994"), fora do padrão dd/mm/aaaa (regra R5). É a data do R-1 ("Santa Cruz do Capibaribe, 08 de fevereiro de 1994"); igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Transmitente Prefeitura Municipal da cópia do R-1 removida; a mesma parte continua na linha 154, ligada ao R-1 que fica.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>PROPRIETARIOS</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>NÃO CONSTA</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>[Maria do Socorro Vieira], brasileira, divorciada, comerciante, residente nesta cidade, portadora do CPF N.º 882.791.114-68</t>
-        </is>
-      </c>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr"/>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Vazio na base. A proprietária na abertura é a transmitente do R-1, Maria do Socorro Vieira, com a qualificação que está no texto do R-1; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Adquirente "José Ramos de Moura" ligado só à cópia do R-1 removida. Nenhum texto desta matrícula, em nenhuma versão, cita esse nome, e o R-1 cujo texto existe ("R.1. MAT. Nº 5.092") tem como adquirente Maria Jozé da Silva.</t>
         </is>
       </c>
     </row>
@@ -16958,22 +16958,22 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>MATRICULA ANTERIOR</t>
+          <t>DATA ABERTURA</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Em virtude de herança dos bens deixados pelo falecimento de José Vieira Filho, conforme formal de Partilha datado de 21</t>
+          <t>08 de fevereiro de 1994</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Em virtude de herança dos bens deixados pelo falecimento de José Vieira Filho, conforme formal de Partilha datado de 21 de novembro de 1985 extraído pelo Escrivão Renato Cordeiro de Arruda dos autos de inventário n.º 1216/84, expedido pelo Juiz de Direito desta Comarca, Dr. Roberto da Silva Maia e registrada sob o N.º R-1-MAT. 4.995, no livro N.º 2BF, às fls. 43 em 07 de novembro de 1991 do Registro Geral de Imóveis desta Comarca. [Rúbrica]</t>
+          <t>08/02/1994</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Texto cortado na base ("...datado de 21"); texto completo igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Data escrita por extenso ("08 de fevereiro de 1994"), fora do padrão dd/mm/aaaa (regra R5). É a data do R-1 ("Santa Cruz do Capibaribe, 08 de fevereiro de 1994"); igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -16990,32 +16990,32 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>MATRÍCULA</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>740</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AREA TOTAL</t>
+          <t>PROPRIETARIOS</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>10,00</t>
+          <t>NÃO CONSTA</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>250,00</t>
+          <t>[Maria do Socorro Vieira], brasileira, divorciada, comerciante, residente nesta cidade, portadora do CPF N.º 882.791.114-68</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>A base trazia 10,00 (só a frente). A descrição diz 10,00 m de frente e de fundos por 25,00 m dos dois lados, ou seja, 250 m²; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Vazio na base. A proprietária na abertura é a transmitente do R-1, Maria do Socorro Vieira, com a qualificação que está no texto do R-1; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17032,32 +17032,32 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>MATRÍCULA</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>740</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>LOGRADOURO</t>
+          <t>MATRICULA ANTERIOR</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>NÃO CONSTA</t>
+          <t>Em virtude de herança dos bens deixados pelo falecimento de José Vieira Filho, conforme formal de Partilha datado de 21</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Rua Cezário Aragão</t>
+          <t>Em virtude de herança dos bens deixados pelo falecimento de José Vieira Filho, conforme formal de Partilha datado de 21 de novembro de 1985 extraído pelo Escrivão Renato Cordeiro de Arruda dos autos de inventário n.º 1216/84, expedido pelo Juiz de Direito desta Comarca, Dr. Roberto da Silva Maia e registrada sob o N.º R-1-MAT. 4.995, no livro N.º 2BF, às fls. 43 em 07 de novembro de 1991 do Registro Geral de Imóveis desta Comarca. [Rúbrica]</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Vazio na base. A descrição diz "dando frente para a Rua Cezário Aragão"; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Texto cortado na base ("...datado de 21"); texto completo igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17084,22 +17084,22 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>TIPO LOGRADOURO ONR</t>
+          <t>AREA TOTAL</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>NÃO CONSTA</t>
+          <t>10,00</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Rua</t>
+          <t>250,00</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Vazio na base. É uma rua (Rua Cezário Aragão); igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>A base trazia 10,00 (só a frente). A descrição diz 10,00 m de frente e de fundos por 25,00 m dos dois lados, ou seja, 250 m²; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>LOGRADOURO</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -17136,12 +17136,12 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>Rua Cezário Aragão</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Vazio na base. A descrição diz "terreno de N.º 390"; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Vazio na base. A descrição diz "dando frente para a Rua Cezário Aragão"; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17168,22 +17168,22 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>DESCRICAO</t>
+          <t>TIPO LOGRADOURO ONR</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>IMÓVEL - 01 (UM) terreno de N.º 390 (Trezentos e noventa), dando frente para a Rua Cezário Aragão nesta cidade, medindo 10,00 metros na parte da frente, 10,00 metros na parte de trás e 25,00 metros de ambos os lados. Limitando-se na parte da frente com o leito da Rua Cezário Aragão, na parte de trás com o terreno de N.º 364, do lado direito com o terreno n.º 400 e do lado esquerdo com o terreno de N.º 386, cujo terreno era composto de 02 (dois) terrenos de N.ºs 390 e 396, dando frente para a ref</t>
+          <t>NÃO CONSTA</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>IMÓVEL - 01 (UM) terreno de N.º 390 (Trezentos e noventa), dando frente para a Rua Cezário Aragão nesta cidade, medindo 10,00 metros na parte da frente, 10,00 metros na parte de trás e 25,00 metros de ambos os lados. Limitando-se na parte da frente com o leito da Rua Cezário Aragão, na parte de trás com o terreno de N.º 364, do lado direito com o terreno n.º 400 e do lado esquerdo com o terreno de N.º 386, cujo terreno era composto de 02 (dois) terrenos de N.ºs 390 e 396, dando frente para a referida rua, medindo cada um 05,00 metros de frente por 25,00 metros de fundos e em virtude de remembramento, os referidos terrenos tornaram-se um só terreno de N.º 390 (trezentos e noventa), já caracterizado acima, conforme planta de remembramento aprovada pela Prefeitura Municipal local em 14 de agosto de 1992, assinada pelo Eng. Civil José Roberval da Silva, arquivada em Cartório</t>
+          <t>Rua</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Texto cortado na base ("...dando frente para a ref"); texto completo (com o remembramento dos terrenos 390 e 396) igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Vazio na base. É uma rua (Rua Cezário Aragão); igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17200,32 +17200,32 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>T. URBANO</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>714</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>03/01/1994</t>
+          <t>NÃO CONSTA</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>08/02/1994</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>A base usava a data errada da escritura ("03 de janeiro de 1994 digo 03 de março de 1993"). O registro foi feito em "Santa Cruz do Capibaribe, 08 de fevereiro de 1994", como diz o fim do texto; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Vazio na base. A descrição diz "terreno de N.º 390"; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17242,32 +17242,32 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>T. URBANO</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>714</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>DESCRICAO</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>15/09/1995</t>
+          <t>IMÓVEL - 01 (UM) terreno de N.º 390 (Trezentos e noventa), dando frente para a Rua Cezário Aragão nesta cidade, medindo 10,00 metros na parte da frente, 10,00 metros na parte de trás e 25,00 metros de ambos os lados. Limitando-se na parte da frente com o leito da Rua Cezário Aragão, na parte de trás com o terreno de N.º 364, do lado direito com o terreno n.º 400 e do lado esquerdo com o terreno de N.º 386, cujo terreno era composto de 02 (dois) terrenos de N.ºs 390 e 396, dando frente para a ref</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>23/10/1995</t>
+          <t>IMÓVEL - 01 (UM) terreno de N.º 390 (Trezentos e noventa), dando frente para a Rua Cezário Aragão nesta cidade, medindo 10,00 metros na parte da frente, 10,00 metros na parte de trás e 25,00 metros de ambos os lados. Limitando-se na parte da frente com o leito da Rua Cezário Aragão, na parte de trás com o terreno de N.º 364, do lado direito com o terreno n.º 400 e do lado esquerdo com o terreno de N.º 386, cujo terreno era composto de 02 (dois) terrenos de N.ºs 390 e 396, dando frente para a referida rua, medindo cada um 05,00 metros de frente por 25,00 metros de fundos e em virtude de remembramento, os referidos terrenos tornaram-se um só terreno de N.º 390 (trezentos e noventa), já caracterizado acima, conforme planta de remembramento aprovada pela Prefeitura Municipal local em 14 de agosto de 1992, assinada pelo Eng. Civil José Roberval da Silva, arquivada em Cartório</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>A base usava a data da escritura (15/09/1995). O registro foi feito em "Santa Cruz do Capibaribe, 23 de outubro de 1995", como diz o fim do texto; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Texto cortado na base ("...dando frente para a ref"); texto completo (com o remembramento dos terrenos 390 e 396) igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -17299,17 +17299,17 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>28/04/2000</t>
+          <t>03/01/1994</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>09/04/2004</t>
+          <t>08/02/1994</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>A base usava a data da assembleia do banco (28/04/2000). A averbação foi feita em "Santa Cruz do Capibaribe - PE, 09 de Abril de 2004", como diz o fim do texto; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>A base usava a data errada da escritura ("03 de janeiro de 1994 digo 03 de março de 1993"). O registro foi feito em "Santa Cruz do Capibaribe, 08 de fevereiro de 1994", como diz o fim do texto; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17331,27 +17331,27 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>HIPOTECA</t>
+          <t>15/09/1995</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE REGISTRO</t>
+          <t>23/10/1995</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>O texto é o pedido do BANDEPE para cancelar o "registro 2, matrícula 5.374" (a hipoteca R-2), e não uma nova hipoteca; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>A base usava a data da escritura (15/09/1995). O registro foi feito em "Santa Cruz do Capibaribe, 23 de outubro de 1995", como diz o fim do texto; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -17383,17 +17383,17 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>29/04/2004</t>
+          <t>28/04/2000</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>03/08/2005</t>
+          <t>09/04/2004</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>A base usava a data da escritura (29/04/2004). O registro foi feito em "Santa Cruz do Capibaribe - PE 03 de agosto de 2005", como diz o fim do texto; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>A base usava a data da assembleia do banco (28/04/2000). A averbação foi feita em "Santa Cruz do Capibaribe - PE, 09 de Abril de 2004", como diz o fim do texto; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17405,25 +17405,37 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>4963</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr"/>
+          <t>2361</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>ATO</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>HIPOTECA</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>CANCELAMENTO DE REGISTRO</t>
+        </is>
+      </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Na base, nenhuma parte tinha ID de ato (todas "NÃO CONSTA"), e por isso o importador rejeitava a matrícula (regra R2). Além disso, os papéis na hipoteca estavam trocados (banco como "Devedor", Hélio como "Credor") e Fernanda tinha o CPF do marido. As partes foram trocadas pela lista completa e ligada a cada ato que está nas outras 3 versões.</t>
+          <t>O texto é o pedido do BANDEPE para cancelar o "registro 2, matrícula 5.374" (a hipoteca R-2), e não uma nova hipoteca; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17435,25 +17447,37 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>4964</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr"/>
+          <t>2362</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>29/04/2004</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>03/08/2005</t>
+        </is>
+      </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Na base, nenhuma parte tinha ID de ato (todas "NÃO CONSTA"), e por isso o importador rejeitava a matrícula (regra R2). Além disso, os papéis na hipoteca estavam trocados (banco como "Devedor", Hélio como "Credor") e Fernanda tinha o CPF do marido. As partes foram trocadas pela lista completa e ligada a cada ato que está nas outras 3 versões.</t>
+          <t>A base usava a data da escritura (29/04/2004). O registro foi feito em "Santa Cruz do Capibaribe - PE 03 de agosto de 2005", como diz o fim do texto; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -17475,7 +17499,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
@@ -17505,7 +17529,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
@@ -17535,7 +17559,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
@@ -17565,7 +17589,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
@@ -17595,7 +17619,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
@@ -17625,7 +17649,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -17650,12 +17674,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -17663,7 +17687,7 @@
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Linha da recuperação automática com dados errados: CIDADE preenchida com o nome da pessoa, Hélio de Souza Lima repetido 4 vezes, Fernanda com o CPF 592.249.244-68 (do marido) e qualificação vazia. Foi trocada pelos cadastros completos das outras versões.</t>
+          <t>Na base, nenhuma parte tinha ID de ato (todas "NÃO CONSTA"), e por isso o importador rejeitava a matrícula (regra R2). Além disso, os papéis na hipoteca estavam trocados (banco como "Devedor", Hélio como "Credor") e Fernanda tinha o CPF do marido. As partes foram trocadas pela lista completa e ligada a cada ato que está nas outras 3 versões.</t>
         </is>
       </c>
     </row>
@@ -17680,12 +17704,12 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -17693,7 +17717,7 @@
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Linha da recuperação automática com dados errados: CIDADE preenchida com o nome da pessoa, Hélio de Souza Lima repetido 4 vezes, Fernanda com o CPF 592.249.244-68 (do marido) e qualificação vazia. Foi trocada pelos cadastros completos das outras versões.</t>
+          <t>Na base, nenhuma parte tinha ID de ato (todas "NÃO CONSTA"), e por isso o importador rejeitava a matrícula (regra R2). Além disso, os papéis na hipoteca estavam trocados (banco como "Devedor", Hélio como "Credor") e Fernanda tinha o CPF do marido. As partes foram trocadas pela lista completa e ligada a cada ato que está nas outras 3 versões.</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17739,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -17745,7 +17769,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -17775,7 +17799,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
@@ -17805,7 +17829,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
@@ -17835,7 +17859,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -17855,17 +17879,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>linha acrescentada</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4975</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -17873,7 +17897,7 @@
       <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Parte ligada ao ato pelo ID, com papel e documento iguais ao texto do ato; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Linha da recuperação automática com dados errados: CIDADE preenchida com o nome da pessoa, Hélio de Souza Lima repetido 4 vezes, Fernanda com o CPF 592.249.244-68 (do marido) e qualificação vazia. Foi trocada pelos cadastros completos das outras versões.</t>
         </is>
       </c>
     </row>
@@ -17885,17 +17909,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>linha acrescentada</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4976</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
@@ -17903,7 +17927,7 @@
       <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Parte ligada ao ato pelo ID, com papel e documento iguais ao texto do ato; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Linha da recuperação automática com dados errados: CIDADE preenchida com o nome da pessoa, Hélio de Souza Lima repetido 4 vezes, Fernanda com o CPF 592.249.244-68 (do marido) e qualificação vazia. Foi trocada pelos cadastros completos das outras versões.</t>
         </is>
       </c>
     </row>
@@ -17925,7 +17949,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4977</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4975</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
@@ -17955,7 +17979,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4978</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4976</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
@@ -17985,7 +18009,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4979</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4977</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
@@ -18015,7 +18039,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4980</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4978</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
@@ -18045,7 +18069,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4981</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4979</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -18075,7 +18099,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4982</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4980</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -18105,7 +18129,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4983</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4981</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
@@ -18135,7 +18159,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4984</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4982</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
@@ -18160,12 +18184,12 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 2476</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4983</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -18173,7 +18197,7 @@
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Cadastro com os dados dos textos (CPF, RG, estado civil, endereço); igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Parte ligada ao ato pelo ID, com papel e documento iguais ao texto do ato; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -18190,12 +18214,12 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 2477</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 4984</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -18203,7 +18227,7 @@
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Cadastro com os dados dos textos (CPF, RG, estado civil, endereço); igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Parte ligada ao ato pelo ID, com papel e documento iguais ao texto do ato; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -18225,7 +18249,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 2478</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 2476</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -18255,7 +18279,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 2479</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 2477</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -18280,12 +18304,12 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>P. JURÍDICA</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 780</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 2478</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -18293,7 +18317,7 @@
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Pessoa jurídica que é parte do R-2/AV-3 e não tinha cadastro na base; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Cadastro com os dados dos textos (CPF, RG, estado civil, endereço); igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -18310,12 +18334,12 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>P. JURÍDICA</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 781</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 2479</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -18323,29 +18347,29 @@
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Pessoa jurídica que é parte do R-2/AV-3 e não tinha cadastro na base; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
+          <t>Cadastro com os dados dos textos (CPF, RG, estado civil, endereço); igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>linha acrescentada</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>P. JURÍDICA</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 780</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -18353,29 +18377,29 @@
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Primeiro "R-3-5.504" (Flávia Gomes Aragão a Camilo Fernandes de Lima Bezerra, ATO "COMPRA E VENDA (CANCELADO)", REGISTRADO "N"). O próprio texto o anula: "NOTA: Em Tempo: Fica esclarecido que o R-3 fica cancelado em virtude de lapso. Santa Cruz do Capibaribe-PE, 20 de junho de 2011". O número 3 ficou com o registro refeito no mesmo dia (Creuza Maria Gomes Aragão aos 4 adquirentes, escritura de 13/08/2010, livro 175). É esse que as matrículas 16618 e 16877 citam como "R.3-Mat(s). 5.503 e 5.504 ... 20 de Junho de 2011".</t>
+          <t>Pessoa jurídica que é parte do R-2/AV-3 e não tinha cadastro na base; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>linha acrescentada</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>P. JURÍDICA</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx linha 781</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -18383,7 +18407,7 @@
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Parte (transmitente Flávia Gomes Aragão) do R-3 cancelado por lapso, que foi removido; Flávia continua como adquirente no R-2.</t>
+          <t>Pessoa jurídica que é parte do R-2/AV-3 e não tinha cadastro na base; igual em "Matriculas_faltantes_PADRAO_CONSOLIDADA.xlsx", "Cópia de PLANILHA SANTA 2-BA a 2-BZ.xlsx" e "Matriculas_PLANILHA_2-AE_a_2-BZ.xlsx".</t>
         </is>
       </c>
     </row>
@@ -18400,12 +18424,12 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -18413,14 +18437,14 @@
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Parte (adquirente Camilo Fernandes de Lima Bezerra) do R-3 cancelado por lapso, que foi removido; Camilo continua como adquirente no R-3 válido.</t>
+          <t>Primeiro "R-3-5.504" (Flávia Gomes Aragão a Camilo Fernandes de Lima Bezerra, ATO "COMPRA E VENDA (CANCELADO)", REGISTRADO "N"). O próprio texto o anula: "NOTA: Em Tempo: Fica esclarecido que o R-3 fica cancelado em virtude de lapso. Santa Cruz do Capibaribe-PE, 20 de junho de 2011". O número 3 ficou com o registro refeito no mesmo dia (Creuza Maria Gomes Aragão aos 4 adquirentes, escritura de 13/08/2010, livro 175). É esse que as matrículas 16618 e 16877 citam como "R.3-Mat(s). 5.503 e 5.504 ... 20 de Junho de 2011".</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -18430,12 +18454,12 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="E391" t="inlineStr"/>
@@ -18443,14 +18467,14 @@
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
-          <t>AV-4 de 15/07/2011 (ATO "DIVISÃO AMIGÁVEL (SEM EFEITO)", REGISTRADO "N", sem partes). O próprio texto diz que esse lançamento da divisão amigável (livro 182, fls 186/186v) ficou "SEM EFEITO em virtude de lapso". A mesma escritura de divisão amigável (livro 182, fls 186 a 186v) foi lançada de novo como R-4-5.831 em 02/09/2011, que é o ato válido e fica com o número 4. Nas versões antigas (Cópia 2-BA a 2-BZ e Matriculas_PLANILHA_2-AE_a_2-BZ) esse mesmo lançamento aparece apenas como "AV-4-5.831 CANCELADO".</t>
+          <t>Parte (transmitente Flávia Gomes Aragão) do R-3 cancelado por lapso, que foi removido; Flávia continua como adquirente no R-2.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -18460,12 +18484,12 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
@@ -18473,14 +18497,14 @@
       <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Primeira "AV-3-5931" (ATO "DESMEMBRAMENTO (CANCELADO)", REGISTRADO "N"). O próprio lançamento foi anulado no livro: o texto termina com "Fica cancelada a AV.3 da presente matrícula" e ainda cita uma planta aprovada em 09.02.1999, data posterior ao próprio lançamento (11/05/1998). O número 3 ficou com a AV-3 válida (desmembramento em lotes 20-A, 20-B e 20-C, planta aprovada em 16/04/1998, eng. Tilmilsom Altamir Cunha), que é a base da AV-4 (novo desmembramento do lote 20-A). A matrícula 13576 confirma a sequência ao citar o "R.2-Mat. 5.931" e o "AV.4-Mat. ... 5.931".</t>
+          <t>Parte (adquirente Camilo Fernandes de Lima Bezerra) do R-3 cancelado por lapso, que foi removido; Camilo continua como adquirente no R-3 válido.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -18490,12 +18514,12 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
@@ -18503,19 +18527,19 @@
       <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Linha repetida: havia duas partes idênticas "Prefeitura Municipal de Santa Cruz do Capibaribe - PE" (Parte, DESMEMBRAMENTO, ID AV-3), uma para cada AV-3. Com a retirada da AV-3 cancelada, fica uma só (linha 8345), ligada à AV-3 válida, junto com Benedito Florentino Pessoa.</t>
+          <t>AV-4 de 15/07/2011 (ATO "DIVISÃO AMIGÁVEL (SEM EFEITO)", REGISTRADO "N", sem partes). O próprio texto diz que esse lançamento da divisão amigável (livro 182, fls 186/186v) ficou "SEM EFEITO em virtude de lapso". A mesma escritura de divisão amigável (livro 182, fls 186 a 186v) foi lançada de novo como R-4-5.831 em 02/09/2011, que é o ato válido e fica com o número 4. Nas versões antigas (Cópia 2-BA a 2-BZ e Matriculas_PLANILHA_2-AE_a_2-BZ) esse mesmo lançamento aparece apenas como "AV-4-5.831 CANCELADO".</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -18525,39 +18549,27 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>4081</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>ORDEM</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>4075</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Consequência da renumeração do Habite-se (que passou a AV-3): a averbação da CND do INSS, da mesma data (27/04/2009) e lançada logo depois do Habite-se no livro ("AV-3-6214"), passa a AV-4 para não repetir o número 3.</t>
+          <t>Primeira "AV-3-5931" (ATO "DESMEMBRAMENTO (CANCELADO)", REGISTRADO "N"). O próprio lançamento foi anulado no livro: o texto termina com "Fica cancelada a AV.3 da presente matrícula" e ainda cita uma planta aprovada em 09.02.1999, data posterior ao próprio lançamento (11/05/1998). O número 3 ficou com a AV-3 válida (desmembramento em lotes 20-A, 20-B e 20-C, planta aprovada em 16/04/1998, eng. Tilmilsom Altamir Cunha), que é a base da AV-4 (novo desmembramento do lote 20-A). A matrícula 13576 confirma a sequência ao citar o "R.2-Mat. 5.931" e o "AV.4-Mat. ... 5.931".</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -18567,27 +18579,15 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>8350</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>AV-3</t>
-        </is>
-      </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>AV-4</t>
-        </is>
-      </c>
+          <t>8344</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Parte (requerente Associação Bíblica e Cultural Amantes da Liberdade) da averbação da CND, renumerada de AV-3 para AV-4.</t>
+          <t>Linha repetida: havia duas partes idênticas "Prefeitura Municipal de Santa Cruz do Capibaribe - PE" (Parte, DESMEMBRAMENTO, ID AV-3), uma para cada AV-3. Com a retirada da AV-3 cancelada, fica uma só (linha 8345), ligada à AV-3 válida, junto com Benedito Florentino Pessoa.</t>
         </is>
       </c>
     </row>
@@ -18609,7 +18609,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -18619,17 +18619,17 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Renumeração por ordem cronológica. O livro tem dois lançamentos "AV-2-6214": a retificação de 06/10/1999 (lote correto nº 25), feita no mesmo dia do R-1, e o Habite-se de 27/04/2009. Como R e AV dividem uma numeração única em ordem cronológica, a retificação de 1999 fica com o 2 e o Habite-se de 2009 passa a 3. Nenhuma outra matrícula cita atos da 6214.</t>
+          <t>Consequência da renumeração do Habite-se (que passou a AV-3): a averbação da CND do INSS, da mesma data (27/04/2009) e lançada logo depois do Habite-se no livro ("AV-3-6214"), passa a AV-4 para não repetir o número 3.</t>
         </is>
       </c>
     </row>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -18661,29 +18661,29 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>AV-2</t>
+          <t>AV-3</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>AV-3</t>
+          <t>AV-4</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Parte (proprietária Associação Bíblica e Cultural Amantes da Liberdade) do Habite-se, renumerado de AV-2 para AV-3.</t>
+          <t>Parte (requerente Associação Bíblica e Cultural Amantes da Liberdade) da averbação da CND, renumerada de AV-3 para AV-4.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -18693,22 +18693,34 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
+          <t>4080</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>ORDEM</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Lançamento "R-2-14347 - CANCELADO" (ATO "CANCELADO", sem data, sem texto próprio, REGISTRADO "N", sem partes). O número 2 é da AV-2 (desmembramento de 17/08/2010 em lotes 15, 15-A, 15-B, 15-C, 15-D e acesso): as matrículas 14725, 14726, 14728 e 17409, abertas para esses lotes, dizem "registrada sob o n.º R.1-Mat. 14.347 ... encontrando-se atualmente averbado sob o n.º AV.2-Mat. 14.347".</t>
+          <t>Renumeração por ordem cronológica. O livro tem dois lançamentos "AV-2-6214": a retificação de 06/10/1999 (lote correto nº 25), feita no mesmo dia do R-1, e o Habite-se de 27/04/2009. Como R e AV dividem uma numeração única em ordem cronológica, a retificação de 1999 fica com o 2 e o Habite-se de 2009 passa a 3. Nenhuma outra matrícula cita atos da 6214.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>14544</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -18718,74 +18730,62 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>ATIVA</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>CANCELADA</t>
+          <t>AV-2</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>ATIVA</t>
+          <t>AV-3</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>O "CANCELADA" vinha do registro anulado da Av. Jatobá. Depois da NOTA, a matrícula tem o R.1 válido (REGISTRADO "S", Robélio Marques de Melo como proprietário atual na própria base) e nenhum ato que a encerre.</t>
+          <t>Parte (proprietária Associação Bíblica e Cultural Amantes da Liberdade) do Habite-se, renumerado de AV-2 para AV-3.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>14544</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>PROPRIETARIOS</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>[Severino Domingos Julião], brasileiro, solteiro, maior, comerciante, residente a Av. Jatobá, n° 219, nesta Cidade, portador do CPF/MF sob o n. 031.921.134-72 e da Cédula de Identidade n. 3.414.298-SSP/PE</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>[Imobiliária Félix Ltda], inscrita no CNPJ/MF sob o n. 08.823.528/0001-72, com sede na Av. Tito Sinésio Aragao, n. 112, Centro, nesta Cidade, neste ato representada por seu sócio-administrador Adolfo Félix da Silva], brasileiro, casado, comerciante, residente a Av. Tito Sinésio Aragao, n. 112, Centro, nesta Cidade, portador do CPF/MF sob o n° 019.274.504-20</t>
-        </is>
-      </c>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr">
         <is>
-          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA.</t>
+          <t>Lançamento "R-2-14347 - CANCELADO" (ATO "CANCELADO", sem data, sem texto próprio, REGISTRADO "N", sem partes). O número 2 é da AV-2 (desmembramento de 17/08/2010 em lotes 15, 15-A, 15-B, 15-C, 15-D e acesso): as matrículas 14725, 14726, 14728 e 17409, abertas para esses lotes, dizem "registrada sob o n.º R.1-Mat. 14.347 ... encontrando-se atualmente averbado sob o n.º AV.2-Mat. 14.347".</t>
         </is>
       </c>
     </row>
@@ -18812,22 +18812,22 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>MATRICULA ANTERIOR</t>
+          <t>ATIVA</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Em virtude de compra feita a [Manoel Néri de França] e sua esposa [Maria de Lourdes Araújo França], por Escritura Pública de Compra e Venda, lavrada nestas notas, pelo Tabelião Público Renato Cordeiro de Arruda, em 08 de Abril de 1976 e registrada sob o n. R.1-Mat. 58, às fls. 94, do Livro n. 3-I</t>
+          <t>CANCELADA</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Em virtude de Escritura Pública de Incorporação, datada de 05 de Novembro de 1982, lavrada nestas notas, pelo Tabelião Público Renato Cordeiro de Arruda e registrada sob o n. R.1-Mat. 2.588, no Livro n. 2-TO, às fls. 23v. [rasurado: em 25 de Julho de 1992], do Registro Geral de Imóveis desta Comarca.</t>
+          <t>ATIVA</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA.</t>
+          <t>O "CANCELADA" vinha do registro anulado da Av. Jatobá. Depois da NOTA, a matrícula tem o R.1 válido (REGISTRADO "S", Robélio Marques de Melo como proprietário atual na própria base) e nenhum ato que a encerre.</t>
         </is>
       </c>
     </row>
@@ -18844,27 +18844,27 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>MATRÍCULA</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>TIPO IMOVEL ONR</t>
+          <t>PROPRIETARIOS</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>[Severino Domingos Julião], brasileiro, solteiro, maior, comerciante, residente a Av. Jatobá, n° 219, nesta Cidade, portador do CPF/MF sob o n. 031.921.134-72 e da Cédula de Identidade n. 3.414.298-SSP/PE</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Terreno/Lote</t>
+          <t>[Imobiliária Félix Ltda], inscrita no CNPJ/MF sob o n. 08.823.528/0001-72, com sede na Av. Tito Sinésio Aragao, n. 112, Centro, nesta Cidade, neste ato representada por seu sócio-administrador Adolfo Félix da Silva], brasileiro, casado, comerciante, residente a Av. Tito Sinésio Aragao, n. 112, Centro, nesta Cidade, portador do CPF/MF sob o n° 019.274.504-20</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -18886,32 +18886,32 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>MATRÍCULA</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>AREA TOTAL</t>
+          <t>MATRICULA ANTERIOR</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>NÃO CONSTA</t>
+          <t>Em virtude de compra feita a [Manoel Néri de França] e sua esposa [Maria de Lourdes Araújo França], por Escritura Pública de Compra e Venda, lavrada nestas notas, pelo Tabelião Público Renato Cordeiro de Arruda, em 08 de Abril de 1976 e registrada sob o n. R.1-Mat. 58, às fls. 94, do Livro n. 3-I</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>125,00</t>
+          <t>Em virtude de Escritura Pública de Incorporação, datada de 05 de Novembro de 1982, lavrada nestas notas, pelo Tabelião Público Renato Cordeiro de Arruda e registrada sob o n. R.1-Mat. 2.588, no Livro n. 2-TO, às fls. 23v. [rasurado: em 25 de Julho de 1992], do Registro Geral de Imóveis desta Comarca.</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA. Área = 05,00 m x 25,00 m, como nos lotes vizinhos da mesma quadra 39 (matrículas 14477 e 14478, AREA TOTAL 125,00).</t>
+          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA.</t>
         </is>
       </c>
     </row>
@@ -18938,17 +18938,17 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>TIPO AREA</t>
+          <t>TIPO IMOVEL ONR</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>NÃO CONSTA</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>Terreno/Lote</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -18980,22 +18980,22 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>LOGRADOURO</t>
+          <t>AREA TOTAL</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Av. Jatobá</t>
+          <t>NÃO CONSTA</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Rua Projetada N. 11</t>
+          <t>125,00</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA. A NOTA diz "Limitando-se na parte da frente com o leito da Rua Projetada N. 11".</t>
+          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA. Área = 05,00 m x 25,00 m, como nos lotes vizinhos da mesma quadra 39 (matrículas 14477 e 14478, AREA TOTAL 125,00).</t>
         </is>
       </c>
     </row>
@@ -19022,7 +19022,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>QUADRA</t>
+          <t>TIPO AREA</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -19064,22 +19064,22 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>LOTE</t>
+          <t>LOGRADOURO</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>NÃO CONSTA</t>
+          <t>Av. Jatobá</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>Rua Projetada N. 11</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA.</t>
+          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA. A NOTA diz "Limitando-se na parte da frente com o leito da Rua Projetada N. 11".</t>
         </is>
       </c>
     </row>
@@ -19106,22 +19106,22 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>QUADRA</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>NÃO CONSTA</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>NÃO CONSTA</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA. A NOTA não dá número de casa.</t>
+          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA.</t>
         </is>
       </c>
     </row>
@@ -19148,17 +19148,17 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>TIPO LOGRADOURO ONR</t>
+          <t>LOTE</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Avenida</t>
+          <t>NÃO CONSTA</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Rua</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -19190,22 +19190,22 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>BAIRRO</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>196</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Loteamento Dona Lila</t>
+          <t>NÃO CONSTA</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA.</t>
+          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA. A NOTA não dá número de casa.</t>
         </is>
       </c>
     </row>
@@ -19232,17 +19232,17 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>DESCRICAO</t>
+          <t>TIPO LOGRADOURO ONR</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>IMÓVEL: 01(um) Imóvel, situado na Av. Jatobá, n° 196 (Cento e noventa e seis), Centro, nesta cidade, medindo, digo, edificado em terreno prédio do patrimônio prediogoso, nesta Cidade, medindo 04,50 metros na parte da frente, 05,50 metros na parte de trás, 28,50 metros do lado direito e 29,50 metros do lado esquerdo, com 02 portas na frente, 01 garagem, 02 salas, 03 quartos, 01 corredor, 01 cozinha, 02 banheiros, 01 porta e 01 janela na parte de trás, 01 área descoberta medindo 01, 00 m x 05,00 metros, sem terreno para muro. Limitando-se na parte da frente com o leito da Av. Jatobá; na parte de trás com o leito da Rua Manoel Moraes da Silva; do lado direito com o imóvel n. 200 e do lado esquerdo com o imóvel n. 190.</t>
+          <t>Avenida</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila, nesta Cidade, medindo 05,00 metros na parte da frente, 05,00 metros na parte de trás e 25,00 metros de ambos os lados. Limitando-se na parte da frente com o leito da Rua Projetada N. 11; na parte de trás com o Lote n. 11; do lado direito com o Lote n. 41 e do lado esquerdo com o Lote n. 43.</t>
+          <t>Rua</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -19259,25 +19259,37 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>T. URBANO</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr"/>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>BAIRRO</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Loteamento Dona Lila</t>
+        </is>
+      </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Primeiro "R.1 Mat. 14.544" (Severino Domingos Julião a Elza Joaquina Julião, casa da Av. Jatobá nº 196, REGISTRADO "N"). O próprio texto o anula: "Fica cancelado o presente registro em virtude de ter pro[...] NOTA: SEM EFEITO". No mesmo dia (06/08/2010) o oficial reabriu a matrícula por NOTA para o lote 42 da quadra 39 do Loteamento Dona Lila e lançou o R.1 válido (Imobiliária Félix Ltda a Robélio Marques de Melo).</t>
+          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA.</t>
         </is>
       </c>
     </row>
@@ -19289,25 +19301,37 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>T. URBANO</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr"/>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>DESCRICAO</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>IMÓVEL: 01(um) Imóvel, situado na Av. Jatobá, n° 196 (Cento e noventa e seis), Centro, nesta cidade, medindo, digo, edificado em terreno prédio do patrimônio prediogoso, nesta Cidade, medindo 04,50 metros na parte da frente, 05,50 metros na parte de trás, 28,50 metros do lado direito e 29,50 metros do lado esquerdo, com 02 portas na frente, 01 garagem, 02 salas, 03 quartos, 01 corredor, 01 cozinha, 02 banheiros, 01 porta e 01 janela na parte de trás, 01 área descoberta medindo 01, 00 m x 05,00 metros, sem terreno para muro. Limitando-se na parte da frente com o leito da Av. Jatobá; na parte de trás com o leito da Rua Manoel Moraes da Silva; do lado direito com o imóvel n. 200 e do lado esquerdo com o imóvel n. 190.</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila, nesta Cidade, medindo 05,00 metros na parte da frente, 05,00 metros na parte de trás e 25,00 metros de ambos os lados. Limitando-se na parte da frente com o leito da Rua Projetada N. 11; na parte de trás com o Lote n. 11; do lado direito com o Lote n. 41 e do lado esquerdo com o Lote n. 43.</t>
+        </is>
+      </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Parte (transmitente Severino Domingos Julião) do R-1 anulado ("SEM EFEITO"), que foi removido.</t>
+          <t>O cabeçalho da base (Severino Domingos Julião, casa da Av. Jatobá nº 196) é o da abertura anulada junto com o primeiro R.1 ("NOTA: SEM EFEITO"). O TEXTO do R.1 válido começa com a NOTA de reabertura da matrícula: "NOTA: IMÓVEL: 01 (um) Lote de Terras de n. 42 (quarenta e dois), situado na Quadra n° 39 (trinta e nove), no Loteamento Dona Lila ... PROPRIETÁRIO: [Imobiliária Félix Ltda] ... TÍTULO ANTERIOR: ...", seguida do "R.1 Mat. 14.544" de Imobiliária Félix a Robélio Marques de Melo. Valor copiado literalmente da NOTA.</t>
         </is>
       </c>
     </row>
@@ -19324,12 +19348,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
@@ -19337,7 +19361,7 @@
       <c r="G414" t="inlineStr"/>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Parte (adquirente Elza Joaquina Juliao) do R-1 anulado ("SEM EFEITO"), que foi removido.</t>
+          <t>Primeiro "R.1 Mat. 14.544" (Severino Domingos Julião a Elza Joaquina Julião, casa da Av. Jatobá nº 196, REGISTRADO "N"). O próprio texto o anula: "Fica cancelado o presente registro em virtude de ter pro[...] NOTA: SEM EFEITO". No mesmo dia (06/08/2010) o oficial reabriu a matrícula por NOTA para o lote 42 da quadra 39 do Loteamento Dona Lila e lançou o R.1 válido (Imobiliária Félix Ltda a Robélio Marques de Melo).</t>
         </is>
       </c>
     </row>
@@ -19354,12 +19378,12 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>677</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
@@ -19367,7 +19391,7 @@
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Severino Domingos Julião só aparecia na abertura anulada e no R-1 "SEM EFEITO" (Av. Jatobá nº 196).</t>
+          <t>Parte (transmitente Severino Domingos Julião) do R-1 anulado ("SEM EFEITO"), que foi removido.</t>
         </is>
       </c>
     </row>
@@ -19384,12 +19408,12 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>678</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
@@ -19397,91 +19421,67 @@
       <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Elza Joaquina Juliao só aparecia no R-1 "SEM EFEITO" (Av. Jatobá nº 196).</t>
+          <t>Parte (adquirente Elza Joaquina Juliao) do R-1 anulado ("SEM EFEITO"), que foi removido.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>PROPRIETARIOS</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>[Imobiliária Nascimento Ltda], com sede na Rua Júlia Aragão, n. 136, nesta Cidade, inscrita no CNPJ/MF sob o n. 35.623.180/0001-42, representada por seus sócios [Maria de Fátima do Nascimento], brasileira, solteira, maior, empresária, residente a Rua João Francisco Aragão, n° 101, 3° andar, Centro, nesta Cidade, portadora do CPF/MF sob o n° 747.530.614-34 e [Luiz Amaro Filho], brasileiro, casado, empresário, residente a Rua Arnaldo Monteiro, n° 18, Bairro Novo, nesta Cidade, portador do CPF/MF sob o n° 195.216.504-00</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>[Sebastiana Nascimento da Silva], brasileira, solteira, maior, do lar, residente à Rua Paraná, n° 344, nesta Cidade, portadora do CPF/MF sob o n° 033.937.444-61 e da Cédula de Identidade n° 6.646.046-SSP/PE, [João Francisco dos Santos], brasileiro, casado com a Sra. [Maria Fernandina das Neves Santos] sob o regime de comunhão parcial de bens, agricultor, residente à Rua Paraná, n° 348, nesta Cidade, portador do CPF/MF sob o n° 012.465.417-77 e da Cédula de Identidade n° 1.169.778-SSP/PB, [Carlos Antônio do Nascimento], brasileiro, solteiro, maior, agricultor, residente à Rua Paraná, n° 350, nesta Cidade, portador do CPF/MF sob o n° 245.581.764-49 e da Cédula de Identidade n° 1.830.010-SSP/PE, [Elizabete Jorge da Silva], brasileira, solteira, maior, agricultora, residente à Rua Paraná, n° 354, nesta Cidade, portadora do CPF/MF sob o n° 935.762.774-04 e da Cédula de Identidade n° 3.529.908-SSP/PE, [Rita Rodrigues de Queva], brasileira, solteira, maior, agricultora, residente à Rua Paraná, n° 358, nesta Cidade, [Elmo Bezerra da Silva] e sua esposa [Maria da Paz Santos], brasileiros, casados, eclesiasticamente, aposentado, residente à Rua Belarmino Pereira, n° 445, nesta Cidade, portadores dos CPF/MF sob os n°s 221.065.024-00 e 421.573.824-53 e das Cédulas de Identidade n°s 6.619.098-SSP/PE e 3.575.742-SSP/PE, [Anaide da Silva Alcântara], brasileira, solteira, maior, do lar, residente à Rua Henrique Dias, n° 161, São Cristóvão, nesta Cidade, portadora do CPF/MF sob o n° 058.684.888-65 e da Cédula de Identidade n° 15.635.813-SSP/SP, [Ivanildo Pereira de Araújo], brasileiro, casado, agricultor, residente à Rua Paraná, n° 348, nesta Cidade, portador do CPF/MF sob o n° 267.593.304-04 e da Cédula de Identidade n° 2.090.956-SSP/PE e [José Marques Araújo], brasileiro, casado, auxiliar de mecânica, residente a Rua Paraná, n° 340, nesta Cidade, portador do CPF/MF sob o n° 688.463.554-15 e da Cédula de Identidade n° 26.630.709-1 SSP/SP</t>
-        </is>
-      </c>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr">
         <is>
-          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA.</t>
+          <t>Severino Domingos Julião só aparecia na abertura anulada e no R-1 "SEM EFEITO" (Av. Jatobá nº 196).</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>MATRICULA ANTERIOR</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>Em virtude de Incorporação feita por [Luiz Amaro do Nascimento] e sua esposa [Maria de Lourdes do Nascimento], por Escritura Pública de Incorporação, datada de 10 de Junho de 1991, lavrada nestas notas, pelo Tabelião Público Renato Cordeiro de Arruda e registrada sob o n° R.1-Mat. 4.976, no Livro n° 2-BF, às fls. 17, em 23 de Agosto de 1991 e Memorial Descritivo registrado sob o n° R.2-Mat. 4.976, no Livro n° 2-BF, às fls. 17, em 03 de Agosto de 1993, do Registro Geral de Imóveis desta Comarca. Santa Cruz do Capibaribe-PE; 09 de Agosto de 2006 Oficial do Registro. SEM EFEITO.</t>
-        </is>
-      </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>Em virtude de Compra feita a Imobiliária Tapeva Ltda, datada em 18 de Maio de 2010, lavrada nestas notas, pelo Tabelião Público Renato Cordeiro de Arruda, no Livro n° 173, às fls. 15 à 16v e registrada sob os n°s R.1-Mats. 14.393 e 14.394, no Livro n° 2-DM, às fls. 121 e 122, em 28 de Junho de 2010, respectivamente, do Registro Geral de Imóveis desta Comarca.</t>
-        </is>
-      </c>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr">
         <is>
-          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA.</t>
+          <t>Elza Joaquina Juliao só aparecia no R-1 "SEM EFEITO" (Av. Jatobá nº 196).</t>
         </is>
       </c>
     </row>
@@ -19498,32 +19498,32 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>MATRÍCULA</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>AREA TOTAL</t>
+          <t>PROPRIETARIOS</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>360,00</t>
+          <t>[Imobiliária Nascimento Ltda], com sede na Rua Júlia Aragão, n. 136, nesta Cidade, inscrita no CNPJ/MF sob o n. 35.623.180/0001-42, representada por seus sócios [Maria de Fátima do Nascimento], brasileira, solteira, maior, empresária, residente a Rua João Francisco Aragão, n° 101, 3° andar, Centro, nesta Cidade, portadora do CPF/MF sob o n° 747.530.614-34 e [Luiz Amaro Filho], brasileiro, casado, empresário, residente a Rua Arnaldo Monteiro, n° 18, Bairro Novo, nesta Cidade, portador do CPF/MF sob o n° 195.216.504-00</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>682,50</t>
+          <t>[Sebastiana Nascimento da Silva], brasileira, solteira, maior, do lar, residente à Rua Paraná, n° 344, nesta Cidade, portadora do CPF/MF sob o n° 033.937.444-61 e da Cédula de Identidade n° 6.646.046-SSP/PE, [João Francisco dos Santos], brasileiro, casado com a Sra. [Maria Fernandina das Neves Santos] sob o regime de comunhão parcial de bens, agricultor, residente à Rua Paraná, n° 348, nesta Cidade, portador do CPF/MF sob o n° 012.465.417-77 e da Cédula de Identidade n° 1.169.778-SSP/PB, [Carlos Antônio do Nascimento], brasileiro, solteiro, maior, agricultor, residente à Rua Paraná, n° 350, nesta Cidade, portador do CPF/MF sob o n° 245.581.764-49 e da Cédula de Identidade n° 1.830.010-SSP/PE, [Elizabete Jorge da Silva], brasileira, solteira, maior, agricultora, residente à Rua Paraná, n° 354, nesta Cidade, portadora do CPF/MF sob o n° 935.762.774-04 e da Cédula de Identidade n° 3.529.908-SSP/PE, [Rita Rodrigues de Queva], brasileira, solteira, maior, agricultora, residente à Rua Paraná, n° 358, nesta Cidade, [Elmo Bezerra da Silva] e sua esposa [Maria da Paz Santos], brasileiros, casados, eclesiasticamente, aposentado, residente à Rua Belarmino Pereira, n° 445, nesta Cidade, portadores dos CPF/MF sob os n°s 221.065.024-00 e 421.573.824-53 e das Cédulas de Identidade n°s 6.619.098-SSP/PE e 3.575.742-SSP/PE, [Anaide da Silva Alcântara], brasileira, solteira, maior, do lar, residente à Rua Henrique Dias, n° 161, São Cristóvão, nesta Cidade, portadora do CPF/MF sob o n° 058.684.888-65 e da Cédula de Identidade n° 15.635.813-SSP/SP, [Ivanildo Pereira de Araújo], brasileiro, casado, agricultor, residente à Rua Paraná, n° 348, nesta Cidade, portador do CPF/MF sob o n° 267.593.304-04 e da Cédula de Identidade n° 2.090.956-SSP/PE e [José Marques Araújo], brasileiro, casado, auxiliar de mecânica, residente a Rua Paraná, n° 340, nesta Cidade, portador do CPF/MF sob o n° 688.463.554-15 e da Cédula de Identidade n° 26.630.709-1 SSP/SP</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA. A NOTA diz "perfazendo um total de 682,50 m²".</t>
+          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA.</t>
         </is>
       </c>
     </row>
@@ -19540,32 +19540,32 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>MATRÍCULA</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>LOGRADOURO</t>
+          <t>MATRICULA ANTERIOR</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Rua Projetada P-9</t>
+          <t>Em virtude de Incorporação feita por [Luiz Amaro do Nascimento] e sua esposa [Maria de Lourdes do Nascimento], por Escritura Pública de Incorporação, datada de 10 de Junho de 1991, lavrada nestas notas, pelo Tabelião Público Renato Cordeiro de Arruda e registrada sob o n° R.1-Mat. 4.976, no Livro n° 2-BF, às fls. 17, em 23 de Agosto de 1991 e Memorial Descritivo registrado sob o n° R.2-Mat. 4.976, no Livro n° 2-BF, às fls. 17, em 03 de Agosto de 1993, do Registro Geral de Imóveis desta Comarca. Santa Cruz do Capibaribe-PE; 09 de Agosto de 2006 Oficial do Registro. SEM EFEITO.</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Rua Paraná</t>
+          <t>Em virtude de Compra feita a Imobiliária Tapeva Ltda, datada em 18 de Maio de 2010, lavrada nestas notas, pelo Tabelião Público Renato Cordeiro de Arruda, no Livro n° 173, às fls. 15 à 16v e registrada sob os n°s R.1-Mats. 14.393 e 14.394, no Livro n° 2-DM, às fls. 121 e 122, em 28 de Junho de 2010, respectivamente, do Registro Geral de Imóveis desta Comarca.</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA. A NOTA diz "Limitando-se na parte da frente com o leito da Rua Paraná".</t>
+          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA.</t>
         </is>
       </c>
     </row>
@@ -19592,22 +19592,22 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>QUADRA</t>
+          <t>AREA TOTAL</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>360,00</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>A-6</t>
+          <t>682,50</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA.</t>
+          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA. A NOTA diz "perfazendo um total de 682,50 m²".</t>
         </is>
       </c>
     </row>
@@ -19634,22 +19634,22 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>LOTE</t>
+          <t>LOGRADOURO</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>Rua Projetada P-9</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Rua Paraná</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA.</t>
+          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA. A NOTA diz "Limitando-se na parte da frente com o leito da Rua Paraná".</t>
         </is>
       </c>
     </row>
@@ -19676,17 +19676,17 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>BAIRRO</t>
+          <t>QUADRA</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Loteamento Santo Amaro</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Loteamento Cruz Alta</t>
+          <t>A-6</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -19718,17 +19718,17 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>DESCRICAO</t>
+          <t>LOTE</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>IMÓVEL: 01 (um) lote de terras de n° 08 (oito), situado na quadra n° "E", no Loteamento Santo Amaro, nesta Cidade, medindo 12,00 metros na parte da frente, 12,00 metros na parte de trás e 30,00 metros de ambos os lados, perfazendo um total de 360,00 m². Limitando-se na parte da frente com o leito da Rua Projetada P-9; na parte de trás com o lote n° 07; do lado direito com o lote n° 09 e do lado esquerdo com o leito da Rua Projetada P-8.</t>
+          <t>08</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta, nesta Cidade, medindo 24,00 metros na parte da frente, 21,50 metros na parte de trás e 30,00 metros de ambos os lados, perfazendo um total de 682,50 m². Limitando-se na parte da frente com o leito da Rua Paraná; na parte de trás com partes dos lotes n°s 10 e 11; do lado direito com o lote n° 14 e do lado esquerdo com o leito da Rua Belarmino Pereira. Cujo lote de terras foi remembrado dos lotes n°s 12 e 13, da referida quadra e loteamento, tornando-se o lote de terras de n° 13, conforme planta de remembramento, assinado pelo Engenheiro Civil Bruno Henrique de Silveira, digo, Telmimon Altominlenha - CREA 166-D/PE e aprovada pela Prefeitura Municipal Local, em 28/03/2004, arquivada neste Cartório.</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -19745,25 +19745,37 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>T. URBANO</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr"/>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>BAIRRO</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Loteamento Santo Amaro</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Loteamento Cruz Alta</t>
+        </is>
+      </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Cópia da AV-1: TEXTO idêntico, caractere por caractere, ao da linha 317 (NOTA de reabertura da matrícula com o lote 13 da quadra A-6, Cruz Alta, seguida da "AV-1" de desmembramento em lotes 13 a 13-H), mesma data 09/08/2010. Só difere em REGISTRADO "N". Fica a linha 317 (REGISTRADO "S"), à qual as 10 partes AV-1 já estão ligadas.</t>
+          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA.</t>
         </is>
       </c>
     </row>
@@ -19775,25 +19787,37 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>T. URBANO</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr"/>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>DESCRICAO</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>IMÓVEL: 01 (um) lote de terras de n° 08 (oito), situado na quadra n° "E", no Loteamento Santo Amaro, nesta Cidade, medindo 12,00 metros na parte da frente, 12,00 metros na parte de trás e 30,00 metros de ambos os lados, perfazendo um total de 360,00 m². Limitando-se na parte da frente com o leito da Rua Projetada P-9; na parte de trás com o lote n° 07; do lado direito com o lote n° 09 e do lado esquerdo com o leito da Rua Projetada P-8.</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta, nesta Cidade, medindo 24,00 metros na parte da frente, 21,50 metros na parte de trás e 30,00 metros de ambos os lados, perfazendo um total de 682,50 m². Limitando-se na parte da frente com o leito da Rua Paraná; na parte de trás com partes dos lotes n°s 10 e 11; do lado direito com o lote n° 14 e do lado esquerdo com o leito da Rua Belarmino Pereira. Cujo lote de terras foi remembrado dos lotes n°s 12 e 13, da referida quadra e loteamento, tornando-se o lote de terras de n° 13, conforme planta de remembramento, assinado pelo Engenheiro Civil Bruno Henrique de Silveira, digo, Telmimon Altominlenha - CREA 166-D/PE e aprovada pela Prefeitura Municipal Local, em 28/03/2004, arquivada neste Cartório.</t>
+        </is>
+      </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Pessoa/empresa que só aparecia na abertura anulada ("SEM EFEITO") da Imobiliária Nascimento Ltda (lote 08, quadra "E", Loteamento Santo Amaro); não é parte de nenhum ato nem do cabeçalho corrigido da 14548. (Maria de Fátima do Nascimento, sócia da Imobiliária Nascimento)</t>
+          <t>O cabeçalho da base é a abertura anulada no livro: a MATRICULA ANTERIOR termina com "Oficial do Registro. SEM EFEITO." No mesmo dia o oficial reabriu a matrícula por NOTA (início do TEXTO da AV-1): "NOTA: IMÓVEL: 01 (um) lote de terras de n° 13 (treze), situado na quadra n° A-6, no Loteamento Cruz Alta ... PROPRIETÁRIOS: ... TÍTULO ANTERIOR: ...". As matrículas 15691, 15872, 15876, 15893, 15897, 15959, 15966 e 16048 (lotes 13 a 13-H da quadra A-6, Cruz Alta) confirmam: "matriculado sob o nº 14.548, no Livro nº 2-DM, às fls. 279, em 09 de Agosto de 2010, encontrando-se atualmente averbado sob o nº AV-1-Mat. 14.548". Valor copiado literalmente da NOTA.</t>
         </is>
       </c>
     </row>
@@ -19810,12 +19834,12 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>316</t>
         </is>
       </c>
       <c r="E427" t="inlineStr"/>
@@ -19823,7 +19847,7 @@
       <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Pessoa/empresa que só aparecia na abertura anulada ("SEM EFEITO") da Imobiliária Nascimento Ltda (lote 08, quadra "E", Loteamento Santo Amaro); não é parte de nenhum ato nem do cabeçalho corrigido da 14548. (Luiz Amaro Filho, sócio da Imobiliária Nascimento)</t>
+          <t>Cópia da AV-1: TEXTO idêntico, caractere por caractere, ao da linha 317 (NOTA de reabertura da matrícula com o lote 13 da quadra A-6, Cruz Alta, seguida da "AV-1" de desmembramento em lotes 13 a 13-H), mesma data 09/08/2010. Só difere em REGISTRADO "N". Fica a linha 317 (REGISTRADO "S"), à qual as 10 partes AV-1 já estão ligadas.</t>
         </is>
       </c>
     </row>
@@ -19840,12 +19864,12 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P. JURÍDICA</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>485</t>
         </is>
       </c>
       <c r="E428" t="inlineStr"/>
@@ -19853,91 +19877,67 @@
       <c r="G428" t="inlineStr"/>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Pessoa/empresa que só aparecia na abertura anulada ("SEM EFEITO") da Imobiliária Nascimento Ltda (lote 08, quadra "E", Loteamento Santo Amaro); não é parte de nenhum ato nem do cabeçalho corrigido da 14548. (Imobiliária Nascimento Ltda)</t>
+          <t>Pessoa/empresa que só aparecia na abertura anulada ("SEM EFEITO") da Imobiliária Nascimento Ltda (lote 08, quadra "E", Loteamento Santo Amaro); não é parte de nenhum ato nem do cabeçalho corrigido da 14548. (Maria de Fátima do Nascimento, sócia da Imobiliária Nascimento)</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>ORDEM</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Locação comercial de 02/06/2011 (Sebastião Zacarias Neto e Cosma Eunice Florêncio a Paquetá Calçados Ltda). O número 3 já é da AV-3 (certidão de averbação da construção, 13/10/2010), cujo texto começa com "AV.3 MAT. 14.801". Como R e AV dividem uma numeração única e esta locação é o primeiro ato depois dos três lançados em 13/10/2010 (R-1, AV-2, AV-3), ela é o 4º ato. O cabeçalho transcrito "R.3- MAT. 14.801" repete o número da AV-3; nenhuma outra fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
+          <t>Pessoa/empresa que só aparecia na abertura anulada ("SEM EFEITO") da Imobiliária Nascimento Ltda (lote 08, quadra "E", Loteamento Santo Amaro); não é parte de nenhum ato nem do cabeçalho corrigido da 14548. (Luiz Amaro Filho, sócio da Imobiliária Nascimento)</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>P. JURÍDICA</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>1172</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>R-3</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>R-4</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Parte (Locador Sebastião Zacarias Neto) da locação comercial de 02/06/2011, renumerada de R-3 para R-4.</t>
+          <t>Pessoa/empresa que só aparecia na abertura anulada ("SEM EFEITO") da Imobiliária Nascimento Ltda (lote 08, quadra "E", Loteamento Santo Amaro); não é parte de nenhum ato nem do cabeçalho corrigido da 14548. (Imobiliária Nascimento Ltda)</t>
         </is>
       </c>
     </row>
@@ -19954,32 +19954,32 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ORDEM</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>R-3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>R-4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Parte (Locadora Cosma Eunice Florêncio) da locação comercial de 02/06/2011, renumerada de R-3 para R-4.</t>
+          <t>Locação comercial de 02/06/2011 (Sebastião Zacarias Neto e Cosma Eunice Florêncio a Paquetá Calçados Ltda). O número 3 já é da AV-3 (certidão de averbação da construção, 13/10/2010), cujo texto começa com "AV.3 MAT. 14.801". Como R e AV dividem uma numeração única e esta locação é o primeiro ato depois dos três lançados em 13/10/2010 (R-1, AV-2, AV-3), ela é o 4º ato. O cabeçalho transcrito "R.3- MAT. 14.801" repete o número da AV-3; nenhuma outra fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -20021,7 +20021,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Parte (Locatária Paquetá Calçados Ltda) da locação comercial de 02/06/2011, renumerada de R-3 para R-4.</t>
+          <t>Parte (Locador Sebastião Zacarias Neto) da locação comercial de 02/06/2011, renumerada de R-3 para R-4.</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -20063,14 +20063,14 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Parte (Representante da Locatária Licoveral Bacher) da locação comercial de 02/06/2011, renumerada de R-3 para R-4.</t>
+          <t>Parte (Locadora Cosma Eunice Florêncio) da locação comercial de 02/06/2011, renumerada de R-3 para R-4.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -20080,39 +20080,39 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>TEXTO</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>AV-2-14903 AV.2-14.903. Por digo, Procede-se a esta averbação para ficar constando que o lote de terras da presente ma trícula foi desmembrado, tornando-se 02 (dois) lotes de terras de nºs 51 e 51-A, situados na quadra "F", no Loteamento Neco Aragão, nesta cidade, com as seguintes características: LOTE Nº 51: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga Rua digo, antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 50 e do lado esquerdo com o lote nº 51-A. LOTE Nº 51-A: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de, 80,00 metros digo 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 51. e do lado esquerdo com o lote nº 52; Conforme planta de des membramento, assinada pelo Engenheiro Civil Jarbas Morais Jataí Marquinho - CREA: 3649- D/PB e aprovada pela Prefeitura Municipal local, em 27/04/2015, arquivada neste Cartório. San ta Cruz do Capibaribe-PE, 22 de Junho de 2015. Eu, [Rúbrica] A Oficiala do Registro. AV-2-14903 AV.2-14.903. CERTIFICO, e dou fé, que o Lote digo, foi aberto Matrícula dos Lotes nºs 51 e 51-A, qual coube a matrículas nºs 24.189 e 24.190; às fls. 256, do Livro nº 2-EX, em 20 de Abril de 2016. Santa Cruz do Capibaribe-PE. 20 de A digo, 20 de Maio de 2016; Santa Cruz do Capibaribe-PE. 20 de Maio de 2016. Eu, [Rúbrica] A Oficiala do Registro.</t>
+          <t>R-3</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>AV-2-14903 AV.2-14.903. Por digo, Procede-se a esta averbação para ficar constando que o lote de terras da presente ma trícula foi desmembrado, tornando-se 02 (dois) lotes de terras de nºs 51 e 51-A, situados na quadra "F", no Loteamento Neco Aragão, nesta cidade, com as seguintes características: LOTE Nº 51: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga Rua digo, antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 50 e do lado esquerdo com o lote nº 51-A. LOTE Nº 51-A: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de, 80,00 metros digo 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 51. e do lado esquerdo com o lote nº 52; Conforme planta de des membramento, assinada pelo Engenheiro Civil Jarbas Morais Jataí Marquinho - CREA: 3649- D/PB e aprovada pela Prefeitura Municipal local, em 27/04/2015, arquivada neste Cartório. San ta Cruz do Capibaribe-PE, 22 de Junho de 2015. Eu, [Rúbrica] A Oficiala do Registro.</t>
+          <t>R-4</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>O TEXTO desta linha e o da linha 697 eram iguais e juntavam dois atos: o desmembramento do lote 51 em 51 e 51-A (assinado em 22 de junho de 2015) e a certidão de abertura das matrículas 24.189 e 24.190 (20 de maio de 2016). Esta linha (DESMEMBRAMENTO, DATA 22/06/2015) ficou só com o trecho do desmembramento, sem alterar nenhuma palavra.</t>
+          <t>Parte (Locatária Paquetá Calçados Ltda) da locação comercial de 02/06/2011, renumerada de R-3 para R-4.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -20122,32 +20122,32 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>TEXTO</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>AV-2-14903 AV.2-14.903. Por digo, Procede-se a esta averbação para ficar constando que o lote de terras da presente ma trícula foi desmembrado, tornando-se 02 (dois) lotes de terras de nºs 51 e 51-A, situados na quadra "F", no Loteamento Neco Aragão, nesta cidade, com as seguintes características: LOTE Nº 51: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga Rua digo, antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 50 e do lado esquerdo com o lote nº 51-A. LOTE Nº 51-A: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de, 80,00 metros digo 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 51. e do lado esquerdo com o lote nº 52; Conforme planta de des membramento, assinada pelo Engenheiro Civil Jarbas Morais Jataí Marquinho - CREA: 3649- D/PB e aprovada pela Prefeitura Municipal local, em 27/04/2015, arquivada neste Cartório. San ta Cruz do Capibaribe-PE, 22 de Junho de 2015. Eu, [Rúbrica] A Oficiala do Registro. AV-2-14903 AV.2-14.903. CERTIFICO, e dou fé, que o Lote digo, foi aberto Matrícula dos Lotes nºs 51 e 51-A, qual coube a matrículas nºs 24.189 e 24.190; às fls. 256, do Livro nº 2-EX, em 20 de Abril de 2016. Santa Cruz do Capibaribe-PE. 20 de A digo, 20 de Maio de 2016; Santa Cruz do Capibaribe-PE. 20 de Maio de 2016. Eu, [Rúbrica] A Oficiala do Registro.</t>
+          <t>R-3</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>AV-2-14903 AV.2-14.903. CERTIFICO, e dou fé, que o Lote digo, foi aberto Matrícula dos Lotes nºs 51 e 51-A, qual coube a matrículas nºs 24.189 e 24.190; às fls. 256, do Livro nº 2-EX, em 20 de Abril de 2016. Santa Cruz do Capibaribe-PE. 20 de A digo, 20 de Maio de 2016; Santa Cruz do Capibaribe-PE. 20 de Maio de 2016. Eu, [Rúbrica] A Oficiala do Registro.</t>
+          <t>R-4</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Mesma junção de dois atos da linha 696. Esta linha (ABERTURA DE MATRÍCULA, DATA 20/05/2016) ficou só com o trecho da certidão de abertura das matrículas 24.189 e 24.190, sem alterar nenhuma palavra.</t>
+          <t>Parte (Representante da Locatária Licoveral Bacher) da locação comercial de 02/06/2011, renumerada de R-3 para R-4.</t>
         </is>
       </c>
     </row>
@@ -20169,34 +20169,34 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>696</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>ORDEM</t>
+          <t>TEXTO</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>AV-2-14903 AV.2-14.903. Por digo, Procede-se a esta averbação para ficar constando que o lote de terras da presente ma trícula foi desmembrado, tornando-se 02 (dois) lotes de terras de nºs 51 e 51-A, situados na quadra "F", no Loteamento Neco Aragão, nesta cidade, com as seguintes características: LOTE Nº 51: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga Rua digo, antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 50 e do lado esquerdo com o lote nº 51-A. LOTE Nº 51-A: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de, 80,00 metros digo 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 51. e do lado esquerdo com o lote nº 52; Conforme planta de des membramento, assinada pelo Engenheiro Civil Jarbas Morais Jataí Marquinho - CREA: 3649- D/PB e aprovada pela Prefeitura Municipal local, em 27/04/2015, arquivada neste Cartório. San ta Cruz do Capibaribe-PE, 22 de Junho de 2015. Eu, [Rúbrica] A Oficiala do Registro. AV-2-14903 AV.2-14.903. CERTIFICO, e dou fé, que o Lote digo, foi aberto Matrícula dos Lotes nºs 51 e 51-A, qual coube a matrículas nºs 24.189 e 24.190; às fls. 256, do Livro nº 2-EX, em 20 de Abril de 2016. Santa Cruz do Capibaribe-PE. 20 de A digo, 20 de Maio de 2016; Santa Cruz do Capibaribe-PE. 20 de Maio de 2016. Eu, [Rúbrica] A Oficiala do Registro.</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>AV-2-14903 AV.2-14.903. Por digo, Procede-se a esta averbação para ficar constando que o lote de terras da presente ma trícula foi desmembrado, tornando-se 02 (dois) lotes de terras de nºs 51 e 51-A, situados na quadra "F", no Loteamento Neco Aragão, nesta cidade, com as seguintes características: LOTE Nº 51: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga Rua digo, antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 50 e do lado esquerdo com o lote nº 51-A. LOTE Nº 51-A: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de, 80,00 metros digo 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 51. e do lado esquerdo com o lote nº 52; Conforme planta de des membramento, assinada pelo Engenheiro Civil Jarbas Morais Jataí Marquinho - CREA: 3649- D/PB e aprovada pela Prefeitura Municipal local, em 27/04/2015, arquivada neste Cartório. San ta Cruz do Capibaribe-PE, 22 de Junho de 2015. Eu, [Rúbrica] A Oficiala do Registro.</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Averbação de 20/05/2016 (abertura das matrículas 24.189 e 24.190 para os lotes 51 e 51-A). O número 2 é do desmembramento de 22/06/2015, que ela pressupõe e que veio antes. Na numeração única R/AV, depois de R-1 (03/11/2010) e AV-2 (22/06/2015), ela é o 3º ato. O cabeçalho transcrito "AV.2-14.903" repete o número anterior; nenhuma fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
+          <t>O TEXTO desta linha e o da linha 697 eram iguais e juntavam dois atos: o desmembramento do lote 51 em 51 e 51-A (assinado em 22 de junho de 2015) e a certidão de abertura das matrículas 24.189 e 24.190 (20 de maio de 2016). Esta linha (DESMEMBRAMENTO, DATA 22/06/2015) ficou só com o trecho do desmembramento, sem alterar nenhuma palavra.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>14903</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -20211,34 +20211,34 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>697</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>ORDEM</t>
+          <t>TEXTO</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>AV-2-14903 AV.2-14.903. Por digo, Procede-se a esta averbação para ficar constando que o lote de terras da presente ma trícula foi desmembrado, tornando-se 02 (dois) lotes de terras de nºs 51 e 51-A, situados na quadra "F", no Loteamento Neco Aragão, nesta cidade, com as seguintes características: LOTE Nº 51: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga Rua digo, antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 50 e do lado esquerdo com o lote nº 51-A. LOTE Nº 51-A: medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 20,00 metros de ambos os lados, perfazendo um total de, 80,00 metros digo 80,00 m²; limitando-se na parte da frente com o leito da Rua Pedro Procópio Ferreira (antiga via Local 05), na parte de trás com o lote nº 10, do lado direito com o lote nº 51. e do lado esquerdo com o lote nº 52; Conforme planta de des membramento, assinada pelo Engenheiro Civil Jarbas Morais Jataí Marquinho - CREA: 3649- D/PB e aprovada pela Prefeitura Municipal local, em 27/04/2015, arquivada neste Cartório. San ta Cruz do Capibaribe-PE, 22 de Junho de 2015. Eu, [Rúbrica] A Oficiala do Registro. AV-2-14903 AV.2-14.903. CERTIFICO, e dou fé, que o Lote digo, foi aberto Matrícula dos Lotes nºs 51 e 51-A, qual coube a matrículas nºs 24.189 e 24.190; às fls. 256, do Livro nº 2-EX, em 20 de Abril de 2016. Santa Cruz do Capibaribe-PE. 20 de A digo, 20 de Maio de 2016; Santa Cruz do Capibaribe-PE. 20 de Maio de 2016. Eu, [Rúbrica] A Oficiala do Registro.</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>AV-2-14903 AV.2-14.903. CERTIFICO, e dou fé, que o Lote digo, foi aberto Matrícula dos Lotes nºs 51 e 51-A, qual coube a matrículas nºs 24.189 e 24.190; às fls. 256, do Livro nº 2-EX, em 20 de Abril de 2016. Santa Cruz do Capibaribe-PE. 20 de A digo, 20 de Maio de 2016; Santa Cruz do Capibaribe-PE. 20 de Maio de 2016. Eu, [Rúbrica] A Oficiala do Registro.</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Desmembramento do lote 14 em lotes 14 e 14-A (12/01/2011). O próprio texto do livro começa com "AV2", e a matrícula 15511 (lote 14-A, aberta em 27/01/2011) diz no título anterior que o imóvel está "averbado sob o nº AV-2-Mat. 15.449, no Livro nº 2-DP, ás fls. 291 em 12 de Janeiro de 2011". Com o número 1 do R-1, a planilha estava com AV-1 por engano.</t>
+          <t>Mesma junção de dois atos da linha 696. Esta linha (ABERTURA DE MATRÍCULA, DATA 20/05/2016) ficou só com o trecho da certidão de abertura das matrículas 24.189 e 24.190, sem alterar nenhuma palavra.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>14903</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -20253,7 +20253,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>697</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Certidão de abertura de matrícula para o lote 14-A (27/01/2011). O próprio texto do livro começa com "AV3", e ela vem depois do desmembramento (AV-2). A planilha estava com AV-2 por engano.</t>
+          <t>Averbação de 20/05/2016 (abertura das matrículas 24.189 e 24.190 para os lotes 51 e 51-A). O número 2 é do desmembramento de 22/06/2015, que ela pressupõe e que veio antes. Na numeração única R/AV, depois de R-1 (03/11/2010) e AV-2 (22/06/2015), ela é o 3º ato. O cabeçalho transcrito "AV.2-14.903" repete o número anterior; nenhuma fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -20295,7 +20295,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>973</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -20305,24 +20305,24 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Hipoteca de 15/09/2011 à Caixa Econômica Federal (R$ 57.000,00, 300 meses). Ela é dada por Jaqueline Barbosa da Silva como "Proprietária", o que ela só passa a ser pela compra registrada no R-4 (venda de Lucivânia Maria de Lima Pereira e José Agostinho Alves Pereira a Jaqueline, mesma data). São dois registros, cada um com o seu fecho e assinatura; a hipoteca vem logo depois da compra, então é o R-5. O cabeçalho transcrito "R.4 Mat 15.882" repete o número da compra. No mesmo cartório, o mesmo tipo de contrato com a Caixa aparece como dois registros seguidos (matrícula 15937: R-3 compra e venda e R-4 alienação fiduciária, ambos de 27/08/2014).</t>
+          <t>Desmembramento do lote 14 em lotes 14 e 14-A (12/01/2011). O próprio texto do livro começa com "AV2", e a matrícula 15511 (lote 14-A, aberta em 27/01/2011) diz no título anterior que o imóvel está "averbado sob o nº AV-2-Mat. 15.449, no Livro nº 2-DP, ás fls. 291 em 12 de Janeiro de 2011". Com o número 1 do R-1, a planilha estava com AV-1 por engano.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -20332,32 +20332,32 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>974</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ORDEM</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>R-4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>R-5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Parte (DEVEDORA HIPOTECANTE JAQUELINE BARBOSA DA SILVA) da hipoteca, renumerada de R-4 para R-5. As partes da compra e venda (linhas 2835-2837) continuam no R-4.</t>
+          <t>Certidão de abertura de matrícula para o lote 14-A (27/01/2011). O próprio texto do livro começa com "AV3", e ela vem depois do desmembramento (AV-2). A planilha estava com AV-2 por engano.</t>
         </is>
       </c>
     </row>
@@ -20374,39 +20374,39 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ORDEM</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>R-4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>R-5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Parte (CREDORA CAIXA ECONÔMICA FEDERAL) da hipoteca, renumerada de R-4 para R-5. As partes da compra e venda (linhas 2835-2837) continuam no R-4.</t>
+          <t>Hipoteca de 15/09/2011 à Caixa Econômica Federal (R$ 57.000,00, 300 meses). Ela é dada por Jaqueline Barbosa da Silva como "Proprietária", o que ela só passa a ser pela compra registrada no R-4 (venda de Lucivânia Maria de Lima Pereira e José Agostinho Alves Pereira a Jaqueline, mesma data). São dois registros, cada um com o seu fecho e assinatura; a hipoteca vem logo depois da compra, então é o R-5. O cabeçalho transcrito "R.4 Mat 15.882" repete o número da compra. No mesmo cartório, o mesmo tipo de contrato com a Caixa aparece como dois registros seguidos (matrícula 15937: R-3 compra e venda e R-4 alienação fiduciária, ambos de 27/08/2014).</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -20416,39 +20416,39 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>ATIVA</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>CANCELADA</t>
+          <t>R-4</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>ATIVA</t>
+          <t>R-5</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>O "CANCELADA" vem do fecho do R-1 ("Fica CANCELADA em virtude de lapso"), que anulou só a abertura feita por engano para o solo 1.328 do Moda Center. A matrícula continuou em uso para o lote 12: AV-1 e AV-2 em 13/01/2014, R-3 e R-4 em 27/08/2014, com alienação fiduciária à Caixa.</t>
+          <t>Parte (DEVEDORA HIPOTECANTE JAQUELINE BARBOSA DA SILVA) da hipoteca, renumerada de R-4 para R-5. As partes da compra e venda (linhas 2835-2837) continuam no R-4.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -20458,32 +20458,32 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>MATRÍCULA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>PROPRIETARIOS</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>[O Município de Santa Cruz do Capibaribe-PE], sob o nº 10.091.569/0001-63</t>
+          <t>R-4</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>[Luiz Carlos Alves de Siqueira], brasileiro, casado, motorista, portador da Cédula de Identidade nº 847.539-SSP/PE, inscrito no CPF/MF sob o nº 839.743.694-49, residente e domiciliado na Rua Belo Horizonte, nº 570, Santa Tereza, nesta cidade</t>
+          <t>R-5</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Proprietário copiado sem mudanças do campo "PROPRIETÁRIO:" da NOTA. A NOTA lançada no livro em 07/06/2011, logo após o R-1 cancelado por lapso, refaz a matrícula 15937 para o imóvel verdadeiro (texto das linhas 1543/1544: "NOTA: IMÓVEL: 01 (um) lote de terra de nº 12 (doze), situado na quadra nº 06 (seis), no Loteamento São Miguel II ... PROPRIETÁRIO: [Luiz Carlos Alves de Siqueira] ... TÍTULO ANTERIOR: ... R-1-Mat. 15.007 ... AV-2-Mat. 15.007 ... 07 de Junho de 2011"). Todos os atos seguintes (habite-se, construção na Rua Olavo Bilac 671, venda a Juliana Gomes de Melo e alienação fiduciária à Caixa) tratam desse lote. A matrícula 15938, aberta no mesmo dia para o lote 12-A (desmembrado do lote 12, mesma origem R-1/AV-2-Mat. 15.007), confronta "do lado esquerdo com o lote n.º 12". A descrição da base (solo 1.328 do Moda Center, do Município) era a da abertura feita por lapso: esse solo já está na matrícula 15933.</t>
+          <t>Parte (CREDORA CAIXA ECONÔMICA FEDERAL) da hipoteca, renumerada de R-4 para R-5. As partes da compra e venda (linhas 2835-2837) continuam no R-4.</t>
         </is>
       </c>
     </row>
@@ -20510,22 +20510,22 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>MATRICULA ANTERIOR</t>
+          <t>ATIVA</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Em virtude de Escritura Pública de Desapropriação amigável datada de 10 de Novembro de 1999, lavrada nestas notas, pelo Tabelião Público Renato Cordeiro de Arruda e registrada sob o nº R.1-Mat. 3.215, às fls. 94, no livro nº 2-AF, em 21 de Dezembro de 1999, encontrando-se atualmente matriculado sob o nº MAT. 7.033, às fls. 152, no livro nº 2-BU, em 26 de Abril de 2002, do Registro Geral de Imóveis desta Comarca. Santa Cruz do Capibaribe-PE. 07 de Junho de 2011.</t>
+          <t>CANCELADA</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Em virtude de Compra feita a [Imobiliária A.C.T. Incorporações Ltda.], por Escritura Pública de Compra e Venda, lavrada nestas notas pelo Tabelião Público Renato Cordeiro de Arruda, às fls. 83/83v, no livro nº 178, em 06 de Dezembro de 2010, e registrada sob o nº R-1-Mat. 15.007, no livro nº 2-DQ, às fls. 150, em 25 de Fevereiro de 2011, encontrando-se atualmente averbado sob o nº AV-2-Mat. 15.007, no livro nº 2-DQ, às fls. 150, em 27 de Abril de 2011, do Registro Geral de Imóveis desta Comarca. Santa Cruz do Capibaribe-PE. 07 de Junho de 2011.</t>
+          <t>ATIVA</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Título anterior copiado sem mudanças do campo "TÍTULO ANTERIOR:" da NOTA.</t>
+          <t>O "CANCELADA" vem do fecho do R-1 ("Fica CANCELADA em virtude de lapso"), que anulou só a abertura feita por engano para o solo 1.328 do Moda Center. A matrícula continuou em uso para o lote 12: AV-1 e AV-2 em 13/01/2014, R-3 e R-4 em 27/08/2014, com alienação fiduciária à Caixa.</t>
         </is>
       </c>
     </row>
@@ -20542,32 +20542,32 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>MATRÍCULA</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>796</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>DESCRICAO</t>
+          <t>PROPRIETARIOS</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>IMÓVEL: 01 (um) saldo de nº 1.328, no Setor nº 04, na Rua nº 13, no Santa Cruz Moda Center, nesta cidade, medindo 02,00 metros na parte da frente, 02,00 metros na parte de trás e 0,90 centímetros de ambos os lados; limitando-se: na parte da frente com a Rua nº 13 na parte de trás com a Rua de Serviço nº 13, do lado direito com o box nº 1327 e do lado esquerdo com a Rua nº 24.</t>
+          <t>[O Município de Santa Cruz do Capibaribe-PE], sob o nº 10.091.569/0001-63</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>IMÓVEL: 01 (um) lote de terra de nº 12 (doze), situado na quadra nº 06 (seis), no Loteamento São Miguel II, nesta cidade, medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 18,00 metros de ambos os lados, limitando-se na parte da frente com o leito da Rua Projetada nº 11, na parte de trás com parte do lote nº 17, do lado direito com o lote nº 12-A e do lado esquerdo com o lote nº 11.</t>
+          <t>[Luiz Carlos Alves de Siqueira], brasileiro, casado, motorista, portador da Cédula de Identidade nº 847.539-SSP/PE, inscrito no CPF/MF sob o nº 839.743.694-49, residente e domiciliado na Rua Belo Horizonte, nº 570, Santa Tereza, nesta cidade</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Descrição copiada sem mudanças do campo "IMÓVEL:" da NOTA (lote 12, quadra 06, Loteamento São Miguel II).</t>
+          <t>Proprietário copiado sem mudanças do campo "PROPRIETÁRIO:" da NOTA. A NOTA lançada no livro em 07/06/2011, logo após o R-1 cancelado por lapso, refaz a matrícula 15937 para o imóvel verdadeiro (texto das linhas 1543/1544: "NOTA: IMÓVEL: 01 (um) lote de terra de nº 12 (doze), situado na quadra nº 06 (seis), no Loteamento São Miguel II ... PROPRIETÁRIO: [Luiz Carlos Alves de Siqueira] ... TÍTULO ANTERIOR: ... R-1-Mat. 15.007 ... AV-2-Mat. 15.007 ... 07 de Junho de 2011"). Todos os atos seguintes (habite-se, construção na Rua Olavo Bilac 671, venda a Juliana Gomes de Melo e alienação fiduciária à Caixa) tratam desse lote. A matrícula 15938, aberta no mesmo dia para o lote 12-A (desmembrado do lote 12, mesma origem R-1/AV-2-Mat. 15.007), confronta "do lado esquerdo com o lote n.º 12". A descrição da base (solo 1.328 do Moda Center, do Município) era a da abertura feita por lapso: esse solo já está na matrícula 15933.</t>
         </is>
       </c>
     </row>
@@ -20584,32 +20584,32 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>T. URBANO</t>
+          <t>MATRÍCULA</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>796</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>AREA TOTAL</t>
+          <t>MATRICULA ANTERIOR</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>Em virtude de Escritura Pública de Desapropriação amigável datada de 10 de Novembro de 1999, lavrada nestas notas, pelo Tabelião Público Renato Cordeiro de Arruda e registrada sob o nº R.1-Mat. 3.215, às fls. 94, no livro nº 2-AF, em 21 de Dezembro de 1999, encontrando-se atualmente matriculado sob o nº MAT. 7.033, às fls. 152, no livro nº 2-BU, em 26 de Abril de 2002, do Registro Geral de Imóveis desta Comarca. Santa Cruz do Capibaribe-PE. 07 de Junho de 2011.</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>72,00</t>
+          <t>Em virtude de Compra feita a [Imobiliária A.C.T. Incorporações Ltda.], por Escritura Pública de Compra e Venda, lavrada nestas notas pelo Tabelião Público Renato Cordeiro de Arruda, às fls. 83/83v, no livro nº 178, em 06 de Dezembro de 2010, e registrada sob o nº R-1-Mat. 15.007, no livro nº 2-DQ, às fls. 150, em 25 de Fevereiro de 2011, encontrando-se atualmente averbado sob o nº AV-2-Mat. 15.007, no livro nº 2-DQ, às fls. 150, em 27 de Abril de 2011, do Registro Geral de Imóveis desta Comarca. Santa Cruz do Capibaribe-PE. 07 de Junho de 2011.</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Lote de 04,00 m x 18,00 m; o habite-se transcrito na AV-1 diz "Área do Terreno: 72,00m²".</t>
+          <t>Título anterior copiado sem mudanças do campo "TÍTULO ANTERIOR:" da NOTA.</t>
         </is>
       </c>
     </row>
@@ -20636,22 +20636,22 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>LOGRADOURO</t>
+          <t>DESCRICAO</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Rua nº 13</t>
+          <t>IMÓVEL: 01 (um) saldo de nº 1.328, no Setor nº 04, na Rua nº 13, no Santa Cruz Moda Center, nesta cidade, medindo 02,00 metros na parte da frente, 02,00 metros na parte de trás e 0,90 centímetros de ambos os lados; limitando-se: na parte da frente com a Rua nº 13 na parte de trás com a Rua de Serviço nº 13, do lado direito com o box nº 1327 e do lado esquerdo com a Rua nº 24.</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Rua Projetada nº 11</t>
+          <t>IMÓVEL: 01 (um) lote de terra de nº 12 (doze), situado na quadra nº 06 (seis), no Loteamento São Miguel II, nesta cidade, medindo 04,00 metros na parte da frente, 04,00 metros na parte de trás e 18,00 metros de ambos os lados, limitando-se na parte da frente com o leito da Rua Projetada nº 11, na parte de trás com parte do lote nº 17, do lado direito com o lote nº 12-A e do lado esquerdo com o lote nº 11.</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>NOTA: "limitando-se na parte da frente com o leito da Rua Projetada nº 11".</t>
+          <t>Descrição copiada sem mudanças do campo "IMÓVEL:" da NOTA (lote 12, quadra 06, Loteamento São Miguel II).</t>
         </is>
       </c>
     </row>
@@ -20678,22 +20678,22 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>QUADRA</t>
+          <t>AREA TOTAL</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>1,80</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>72,00</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>NOTA: "situado na quadra nº 06 (seis)".</t>
+          <t>Lote de 04,00 m x 18,00 m; o habite-se transcrito na AV-1 diz "Área do Terreno: 72,00m²".</t>
         </is>
       </c>
     </row>
@@ -20720,22 +20720,22 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>LOTE</t>
+          <t>LOGRADOURO</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>Rua nº 13</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Rua Projetada nº 11</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>NOTA: "lote de terra de nº 12 (doze)".</t>
+          <t>NOTA: "limitando-se na parte da frente com o leito da Rua Projetada nº 11".</t>
         </is>
       </c>
     </row>
@@ -20762,22 +20762,22 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>BAIRRO</t>
+          <t>QUADRA</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Santa Cruz Moda Center</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>São Miguel II</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>NOTA: "no Loteamento São Miguel II". Mesma grafia da matrícula vizinha 15938 (lote 12-A).</t>
+          <t>NOTA: "situado na quadra nº 06 (seis)".</t>
         </is>
       </c>
     </row>
@@ -20789,25 +20789,37 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>T. URBANO</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>1542</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
-      <c r="G451" t="inlineStr"/>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>LOTE</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>R-1 (concessão de direito real de uso do solo 1.328 do Moda Center pelo Município a José Trajano da Silva Júnior e Fernanda Rafaela de Lucena Trajano), cancelado no próprio livro: o texto termina com "Fica CANCELADA em virtude de lapso". A mesma concessão (escritura de 16/02/2011, livro 180, fls. 23 a 24) já estava registrada como R-1 da matrícula 15933 (solo 1.328, setor 04, Rua nº 13, aberta em 03/06/2011). Depois da NOTA, o livro recomeça a numeração em Av.1, Av.2, R3, R4, então o número 1 fica com a AV-1 (habite-se).</t>
+          <t>NOTA: "lote de terra de nº 12 (doze)".</t>
         </is>
       </c>
     </row>
@@ -20819,25 +20831,37 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>T. URBANO</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>1543</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
-      <c r="G452" t="inlineStr"/>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>BAIRRO</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Santa Cruz Moda Center</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>São Miguel II</t>
+        </is>
+      </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Cópia da linha 1544: mesmo TEXTO (a NOTA de 07/06/2011 seguida da "Av. 1-15.937", habite-se de 13/01/2014). A NOTA não é ato numerado: é a reabertura da matrícula, e o seu conteúdo foi para MATRÍCULA e T. URBANO. O número 1 é da "Av. 1-15.937", que continua na linha 1544 (HABITE-SE, 13/01/2014), com o texto completo.</t>
+          <t>NOTA: "no Loteamento São Miguel II". Mesma grafia da matrícula vizinha 15938 (lote 12-A).</t>
         </is>
       </c>
     </row>
@@ -20854,12 +20878,12 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
@@ -20867,7 +20891,7 @@
       <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Parte (concedente Município de Santa Cruz do Capibaribe-PE) do R-1 cancelado por lapso, que foi removido; essa concessão é da matrícula 15933.</t>
+          <t>R-1 (concessão de direito real de uso do solo 1.328 do Moda Center pelo Município a José Trajano da Silva Júnior e Fernanda Rafaela de Lucena Trajano), cancelado no próprio livro: o texto termina com "Fica CANCELADA em virtude de lapso". A mesma concessão (escritura de 16/02/2011, livro 180, fls. 23 a 24) já estava registrada como R-1 da matrícula 15933 (solo 1.328, setor 04, Rua nº 13, aberta em 03/06/2011). Depois da NOTA, o livro recomeça a numeração em Av.1, Av.2, R3, R4, então o número 1 fica com a AV-1 (habite-se).</t>
         </is>
       </c>
     </row>
@@ -20884,12 +20908,12 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
@@ -20897,7 +20921,7 @@
       <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Parte (concessionário José Trajano da Silva Júnior) do R-1 cancelado por lapso, que foi removido; essa concessão é da matrícula 15933.</t>
+          <t>Cópia da linha 1544: mesmo TEXTO (a NOTA de 07/06/2011 seguida da "Av. 1-15.937", habite-se de 13/01/2014). A NOTA não é ato numerado: é a reabertura da matrícula, e o seu conteúdo foi para MATRÍCULA e T. URBANO. O número 1 é da "Av. 1-15.937", que continua na linha 1544 (HABITE-SE, 13/01/2014), com o texto completo.</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20943,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="E455" t="inlineStr"/>
@@ -20927,7 +20951,7 @@
       <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Parte (concessionária Fernanda Rafaela de Lucena Trajano) do R-1 cancelado por lapso, que foi removido; essa concessão é da matrícula 15933.</t>
+          <t>Parte (concedente Município de Santa Cruz do Capibaribe-PE) do R-1 cancelado por lapso, que foi removido; essa concessão é da matrícula 15933.</t>
         </is>
       </c>
     </row>
@@ -20949,7 +20973,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="E456" t="inlineStr"/>
@@ -20957,7 +20981,7 @@
       <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Parte (Luiz Carlos Alves de Siqueira, proprietário) da linha 1543, removida como cópia. A mesma parte continua na AV-1 (linha 2964).</t>
+          <t>Parte (concessionário José Trajano da Silva Júnior) do R-1 cancelado por lapso, que foi removido; essa concessão é da matrícula 15933.</t>
         </is>
       </c>
     </row>
@@ -20974,12 +20998,12 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
@@ -20987,7 +21011,7 @@
       <c r="G457" t="inlineStr"/>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Antônio Figueirôa de Siqueira (prefeito que representou o Município) só aparecia no R-1 cancelado por lapso (concessão que é da matrícula 15933).</t>
+          <t>Parte (concessionária Fernanda Rafaela de Lucena Trajano) do R-1 cancelado por lapso, que foi removido; essa concessão é da matrícula 15933.</t>
         </is>
       </c>
     </row>
@@ -21004,12 +21028,12 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>P. FÍSICA</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -21017,7 +21041,7 @@
       <c r="G458" t="inlineStr"/>
       <c r="H458" t="inlineStr">
         <is>
-          <t>José Trajano da Silva Júnior só aparecia no R-1 cancelado por lapso (concessão que é da matrícula 15933).</t>
+          <t>Parte (Luiz Carlos Alves de Siqueira, proprietário) da linha 1543, removida como cópia. A mesma parte continua na AV-1 (linha 2964).</t>
         </is>
       </c>
     </row>
@@ -21039,7 +21063,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
@@ -21047,7 +21071,7 @@
       <c r="G459" t="inlineStr"/>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Fernanda Rafaela de Lucena Trajano só aparecia no R-1 cancelado por lapso (concessão que é da matrícula 15933).</t>
+          <t>Antônio Figueirôa de Siqueira (prefeito que representou o Município) só aparecia no R-1 cancelado por lapso (concessão que é da matrícula 15933).</t>
         </is>
       </c>
     </row>
@@ -21064,12 +21088,12 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>P. JURÍDICA</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -21077,91 +21101,67 @@
       <c r="G460" t="inlineStr"/>
       <c r="H460" t="inlineStr">
         <is>
-          <t>O Município de Santa Cruz do Capibaribe-PE só aparecia no R-1 cancelado por lapso e na abertura feita por engano (solo 1.328 do Moda Center, matrícula 15933).</t>
+          <t>José Trajano da Silva Júnior só aparecia no R-1 cancelado por lapso (concessão que é da matrícula 15933).</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>P. FÍSICA</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>TEXTO</t>
-        </is>
-      </c>
-      <c r="F461" t="inlineStr">
-        <is>
-          <t>R-2-15957 R-2-Mat. 15.957 Por Escritura Pública de Reti-ratificação e Ratificação, datada em 03 de Janeiro de 2011, lavrada nestas notas, às fls. 26 a 27, do livro n° 179, pelo Tabelião Público Renato Cordeiro de Arruda, o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o n° 10.091.569/0001-63, com sede na Av. Padre Zuzinha, n° 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Aris Aragão, n° 63, nesta Cidade, portador do CPF/MF sob os n°s 363.437.224-91 e da Cédula de Identidade n° 2.662.495-SSP/PE, concedeu aos Concessionários [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da Comunhão parcial de bens, comerciantes, residentes à Rua D. Pedro I, n° 159, Dona Dom, nesta Cidade, portadores do CPF/MF sob os n°s 551.741.324-20 e 032.132.834-52 e das Cédulas de Identidades n°s 3.287.170-SSP/PE e 5.790.073-SSP/PE, respectivamente, o direito real de uso do solo n° 1.522, no setor n° 03, na Rua n° 16, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na escritura lavrada em 13 de Agosto de 2003, no livro n° 127, às fls. 146v/147v, que era Superfície de Área. Santa Cruz do Capibaribe-PE, 10 de Junho de 2011. Eu, [Rúbrica] o Oficial. R-2-15957 R.2-Mat. 15.957 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 10 de Junho de 2011, lavrada nestas notas às fls no 184 a 184v, do Livro no 182, pelo Tabelião Pública 2º Substituta Fernanda Carneiro de Arruda; Os Concedentes [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da comunhão parcial de bens, comerciantes, residentes e domiciliados à Rua Dom Pedro, no 159, Dona Dom, nesta cidade, inscrito no CPF/MF sob o no 551.741.324-20 e 032.132.834-52 e portadores das cédulas de Identidade nos 3.287.170-SSP/PE e 5.790.073-SSP/PE, concedeu ao Concessionário: [Otávio Patrocínio Julião Filho], brasileiro, solteiro, maior, agricultor, residente e domiciliado no Sítio Logradouro, do Município de Sairé, digo, Brejo da Madre de Deus-PE, o direito real de uso do solo no 1.522, no setor no 03, na Rua no 16, no Santa Cruz Moda Center, nesta cidade; para fins comerciais, a título gratuito. Santa Cruz do Capibaribe-PE. 14 de Setembro de 2011. Eu, [Rúbrica] O Oficial do Registro.</t>
-        </is>
-      </c>
-      <c r="G461" t="inlineStr">
-        <is>
-          <t>R-2-15957 R-2-Mat. 15.957 Por Escritura Pública de Reti-ratificação e Ratificação, datada em 03 de Janeiro de 2011, lavrada nestas notas, às fls. 26 a 27, do livro n° 179, pelo Tabelião Público Renato Cordeiro de Arruda, o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o n° 10.091.569/0001-63, com sede na Av. Padre Zuzinha, n° 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Aris Aragão, n° 63, nesta Cidade, portador do CPF/MF sob os n°s 363.437.224-91 e da Cédula de Identidade n° 2.662.495-SSP/PE, concedeu aos Concessionários [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da Comunhão parcial de bens, comerciantes, residentes à Rua D. Pedro I, n° 159, Dona Dom, nesta Cidade, portadores do CPF/MF sob os n°s 551.741.324-20 e 032.132.834-52 e das Cédulas de Identidades n°s 3.287.170-SSP/PE e 5.790.073-SSP/PE, respectivamente, o direito real de uso do solo n° 1.522, no setor n° 03, na Rua n° 16, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na escritura lavrada em 13 de Agosto de 2003, no livro n° 127, às fls. 146v/147v, que era Superfície de Área. Santa Cruz do Capibaribe-PE, 10 de Junho de 2011. Eu, [Rúbrica] o Oficial.</t>
-        </is>
-      </c>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr">
         <is>
-          <t>O TEXTO desta linha e o da linha 1562 eram iguais e juntavam dois registros: a reti-ratificação da escritura de 2003 (Município aos concessionários Severino Adilson da Costa e Adeilza Maria Costa, assinada em 10 de junho de 2011) e a nova concessão de direito real de uso de Severino e Adeilza a Otávio Patrocínio Julião Filho (14 de setembro de 2011). Esta linha (RETI-RATIFICAÇÃO E RATIFICAÇÃO, DATA 10/06/2011) ficou só com o trecho da reti-ratificação, sem alterar nenhuma palavra.</t>
+          <t>Fernanda Rafaela de Lucena Trajano só aparecia no R-1 cancelado por lapso (concessão que é da matrícula 15933).</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>P. JURÍDICA</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>1562</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>TEXTO</t>
-        </is>
-      </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>R-2-15957 R-2-Mat. 15.957 Por Escritura Pública de Reti-ratificação e Ratificação, datada em 03 de Janeiro de 2011, lavrada nestas notas, às fls. 26 a 27, do livro n° 179, pelo Tabelião Público Renato Cordeiro de Arruda, o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o n° 10.091.569/0001-63, com sede na Av. Padre Zuzinha, n° 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Aris Aragão, n° 63, nesta Cidade, portador do CPF/MF sob os n°s 363.437.224-91 e da Cédula de Identidade n° 2.662.495-SSP/PE, concedeu aos Concessionários [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da Comunhão parcial de bens, comerciantes, residentes à Rua D. Pedro I, n° 159, Dona Dom, nesta Cidade, portadores do CPF/MF sob os n°s 551.741.324-20 e 032.132.834-52 e das Cédulas de Identidades n°s 3.287.170-SSP/PE e 5.790.073-SSP/PE, respectivamente, o direito real de uso do solo n° 1.522, no setor n° 03, na Rua n° 16, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na escritura lavrada em 13 de Agosto de 2003, no livro n° 127, às fls. 146v/147v, que era Superfície de Área. Santa Cruz do Capibaribe-PE, 10 de Junho de 2011. Eu, [Rúbrica] o Oficial. R-2-15957 R.2-Mat. 15.957 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 10 de Junho de 2011, lavrada nestas notas às fls no 184 a 184v, do Livro no 182, pelo Tabelião Pública 2º Substituta Fernanda Carneiro de Arruda; Os Concedentes [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da comunhão parcial de bens, comerciantes, residentes e domiciliados à Rua Dom Pedro, no 159, Dona Dom, nesta cidade, inscrito no CPF/MF sob o no 551.741.324-20 e 032.132.834-52 e portadores das cédulas de Identidade nos 3.287.170-SSP/PE e 5.790.073-SSP/PE, concedeu ao Concessionário: [Otávio Patrocínio Julião Filho], brasileiro, solteiro, maior, agricultor, residente e domiciliado no Sítio Logradouro, do Município de Sairé, digo, Brejo da Madre de Deus-PE, o direito real de uso do solo no 1.522, no setor no 03, na Rua no 16, no Santa Cruz Moda Center, nesta cidade; para fins comerciais, a título gratuito. Santa Cruz do Capibaribe-PE. 14 de Setembro de 2011. Eu, [Rúbrica] O Oficial do Registro.</t>
-        </is>
-      </c>
-      <c r="G462" t="inlineStr">
-        <is>
-          <t>R-2-15957 R.2-Mat. 15.957 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 10 de Junho de 2011, lavrada nestas notas às fls no 184 a 184v, do Livro no 182, pelo Tabelião Pública 2º Substituta Fernanda Carneiro de Arruda; Os Concedentes [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da comunhão parcial de bens, comerciantes, residentes e domiciliados à Rua Dom Pedro, no 159, Dona Dom, nesta cidade, inscrito no CPF/MF sob o no 551.741.324-20 e 032.132.834-52 e portadores das cédulas de Identidade nos 3.287.170-SSP/PE e 5.790.073-SSP/PE, concedeu ao Concessionário: [Otávio Patrocínio Julião Filho], brasileiro, solteiro, maior, agricultor, residente e domiciliado no Sítio Logradouro, do Município de Sairé, digo, Brejo da Madre de Deus-PE, o direito real de uso do solo no 1.522, no setor no 03, na Rua no 16, no Santa Cruz Moda Center, nesta cidade; para fins comerciais, a título gratuito. Santa Cruz do Capibaribe-PE. 14 de Setembro de 2011. Eu, [Rúbrica] O Oficial do Registro.</t>
-        </is>
-      </c>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr"/>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Mesma junção de dois registros da linha 1561. Esta linha (CONCESSÃO DE DIREITO REAL DE USO, DATA 14/09/2011) ficou só com o trecho da concessão a Otávio Patrocínio Julião Filho, sem alterar nenhuma palavra.</t>
+          <t>O Município de Santa Cruz do Capibaribe-PE só aparecia no R-1 cancelado por lapso e na abertura feita por engano (solo 1.328 do Moda Center, matrícula 15933).</t>
         </is>
       </c>
     </row>
@@ -21183,27 +21183,27 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>ORDEM</t>
+          <t>TEXTO</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>R-2-15957 R-2-Mat. 15.957 Por Escritura Pública de Reti-ratificação e Ratificação, datada em 03 de Janeiro de 2011, lavrada nestas notas, às fls. 26 a 27, do livro n° 179, pelo Tabelião Público Renato Cordeiro de Arruda, o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o n° 10.091.569/0001-63, com sede na Av. Padre Zuzinha, n° 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Aris Aragão, n° 63, nesta Cidade, portador do CPF/MF sob os n°s 363.437.224-91 e da Cédula de Identidade n° 2.662.495-SSP/PE, concedeu aos Concessionários [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da Comunhão parcial de bens, comerciantes, residentes à Rua D. Pedro I, n° 159, Dona Dom, nesta Cidade, portadores do CPF/MF sob os n°s 551.741.324-20 e 032.132.834-52 e das Cédulas de Identidades n°s 3.287.170-SSP/PE e 5.790.073-SSP/PE, respectivamente, o direito real de uso do solo n° 1.522, no setor n° 03, na Rua n° 16, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na escritura lavrada em 13 de Agosto de 2003, no livro n° 127, às fls. 146v/147v, que era Superfície de Área. Santa Cruz do Capibaribe-PE, 10 de Junho de 2011. Eu, [Rúbrica] o Oficial. R-2-15957 R.2-Mat. 15.957 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 10 de Junho de 2011, lavrada nestas notas às fls no 184 a 184v, do Livro no 182, pelo Tabelião Pública 2º Substituta Fernanda Carneiro de Arruda; Os Concedentes [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da comunhão parcial de bens, comerciantes, residentes e domiciliados à Rua Dom Pedro, no 159, Dona Dom, nesta cidade, inscrito no CPF/MF sob o no 551.741.324-20 e 032.132.834-52 e portadores das cédulas de Identidade nos 3.287.170-SSP/PE e 5.790.073-SSP/PE, concedeu ao Concessionário: [Otávio Patrocínio Julião Filho], brasileiro, solteiro, maior, agricultor, residente e domiciliado no Sítio Logradouro, do Município de Sairé, digo, Brejo da Madre de Deus-PE, o direito real de uso do solo no 1.522, no setor no 03, na Rua no 16, no Santa Cruz Moda Center, nesta cidade; para fins comerciais, a título gratuito. Santa Cruz do Capibaribe-PE. 14 de Setembro de 2011. Eu, [Rúbrica] O Oficial do Registro.</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>R-2-15957 R-2-Mat. 15.957 Por Escritura Pública de Reti-ratificação e Ratificação, datada em 03 de Janeiro de 2011, lavrada nestas notas, às fls. 26 a 27, do livro n° 179, pelo Tabelião Público Renato Cordeiro de Arruda, o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o n° 10.091.569/0001-63, com sede na Av. Padre Zuzinha, n° 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Aris Aragão, n° 63, nesta Cidade, portador do CPF/MF sob os n°s 363.437.224-91 e da Cédula de Identidade n° 2.662.495-SSP/PE, concedeu aos Concessionários [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da Comunhão parcial de bens, comerciantes, residentes à Rua D. Pedro I, n° 159, Dona Dom, nesta Cidade, portadores do CPF/MF sob os n°s 551.741.324-20 e 032.132.834-52 e das Cédulas de Identidades n°s 3.287.170-SSP/PE e 5.790.073-SSP/PE, respectivamente, o direito real de uso do solo n° 1.522, no setor n° 03, na Rua n° 16, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na escritura lavrada em 13 de Agosto de 2003, no livro n° 127, às fls. 146v/147v, que era Superfície de Área. Santa Cruz do Capibaribe-PE, 10 de Junho de 2011. Eu, [Rúbrica] o Oficial.</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Concessão de direito real de uso de 14/09/2011 (Severino Adilson da Costa e Adeilza Maria Costa a Otávio Patrocínio Julião Filho). Ela só é possível depois do R-2 de 10/06/2011, que reconheceu Severino e Adeilza como concessionários do Município. Na numeração única R/AV (AV-1 e R-2 em 10/06/2011), ela é o 3º ato. O cabeçalho transcrito "R.2-Mat. 15.957" repete o número anterior; nenhuma fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
+          <t>O TEXTO desta linha e o da linha 1562 eram iguais e juntavam dois registros: a reti-ratificação da escritura de 2003 (Município aos concessionários Severino Adilson da Costa e Adeilza Maria Costa, assinada em 10 de junho de 2011) e a nova concessão de direito real de uso de Severino e Adeilza a Otávio Patrocínio Julião Filho (14 de setembro de 2011). Esta linha (RETI-RATIFICAÇÃO E RATIFICAÇÃO, DATA 10/06/2011) ficou só com o trecho da reti-ratificação, sem alterar nenhuma palavra.</t>
         </is>
       </c>
     </row>
@@ -21220,32 +21220,32 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>TEXTO</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>R-2</t>
+          <t>R-2-15957 R-2-Mat. 15.957 Por Escritura Pública de Reti-ratificação e Ratificação, datada em 03 de Janeiro de 2011, lavrada nestas notas, às fls. 26 a 27, do livro n° 179, pelo Tabelião Público Renato Cordeiro de Arruda, o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o n° 10.091.569/0001-63, com sede na Av. Padre Zuzinha, n° 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Aris Aragão, n° 63, nesta Cidade, portador do CPF/MF sob os n°s 363.437.224-91 e da Cédula de Identidade n° 2.662.495-SSP/PE, concedeu aos Concessionários [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da Comunhão parcial de bens, comerciantes, residentes à Rua D. Pedro I, n° 159, Dona Dom, nesta Cidade, portadores do CPF/MF sob os n°s 551.741.324-20 e 032.132.834-52 e das Cédulas de Identidades n°s 3.287.170-SSP/PE e 5.790.073-SSP/PE, respectivamente, o direito real de uso do solo n° 1.522, no setor n° 03, na Rua n° 16, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na escritura lavrada em 13 de Agosto de 2003, no livro n° 127, às fls. 146v/147v, que era Superfície de Área. Santa Cruz do Capibaribe-PE, 10 de Junho de 2011. Eu, [Rúbrica] o Oficial. R-2-15957 R.2-Mat. 15.957 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 10 de Junho de 2011, lavrada nestas notas às fls no 184 a 184v, do Livro no 182, pelo Tabelião Pública 2º Substituta Fernanda Carneiro de Arruda; Os Concedentes [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da comunhão parcial de bens, comerciantes, residentes e domiciliados à Rua Dom Pedro, no 159, Dona Dom, nesta cidade, inscrito no CPF/MF sob o no 551.741.324-20 e 032.132.834-52 e portadores das cédulas de Identidade nos 3.287.170-SSP/PE e 5.790.073-SSP/PE, concedeu ao Concessionário: [Otávio Patrocínio Julião Filho], brasileiro, solteiro, maior, agricultor, residente e domiciliado no Sítio Logradouro, do Município de Sairé, digo, Brejo da Madre de Deus-PE, o direito real de uso do solo no 1.522, no setor no 03, na Rua no 16, no Santa Cruz Moda Center, nesta cidade; para fins comerciais, a título gratuito. Santa Cruz do Capibaribe-PE. 14 de Setembro de 2011. Eu, [Rúbrica] O Oficial do Registro.</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>R-3</t>
+          <t>R-2-15957 R.2-Mat. 15.957 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 10 de Junho de 2011, lavrada nestas notas às fls no 184 a 184v, do Livro no 182, pelo Tabelião Pública 2º Substituta Fernanda Carneiro de Arruda; Os Concedentes [Severino Adilson da Costa] e sua esposa [Adeilza Maria Costa], brasileiros, casados sob o regime da comunhão parcial de bens, comerciantes, residentes e domiciliados à Rua Dom Pedro, no 159, Dona Dom, nesta cidade, inscrito no CPF/MF sob o no 551.741.324-20 e 032.132.834-52 e portadores das cédulas de Identidade nos 3.287.170-SSP/PE e 5.790.073-SSP/PE, concedeu ao Concessionário: [Otávio Patrocínio Julião Filho], brasileiro, solteiro, maior, agricultor, residente e domiciliado no Sítio Logradouro, do Município de Sairé, digo, Brejo da Madre de Deus-PE, o direito real de uso do solo no 1.522, no setor no 03, na Rua no 16, no Santa Cruz Moda Center, nesta cidade; para fins comerciais, a título gratuito. Santa Cruz do Capibaribe-PE. 14 de Setembro de 2011. Eu, [Rúbrica] O Oficial do Registro.</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Parte (Concedente Severino Adilson da Costa) da concessão de 14/09/2011, renumerada de R-2 para R-3.</t>
+          <t>Mesma junção de dois registros da linha 1561. Esta linha (CONCESSÃO DE DIREITO REAL DE USO, DATA 14/09/2011) ficou só com o trecho da concessão a Otávio Patrocínio Julião Filho, sem alterar nenhuma palavra.</t>
         </is>
       </c>
     </row>
@@ -21262,32 +21262,32 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ORDEM</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>R-2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>R-3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Parte (Concedente Adeilza Maria Costa) da concessão de 14/09/2011, renumerada de R-2 para R-3.</t>
+          <t>Concessão de direito real de uso de 14/09/2011 (Severino Adilson da Costa e Adeilza Maria Costa a Otávio Patrocínio Julião Filho). Ela só é possível depois do R-2 de 10/06/2011, que reconheceu Severino e Adeilza como concessionários do Município. Na numeração única R/AV (AV-1 e R-2 em 10/06/2011), ela é o 3º ato. O cabeçalho transcrito "R.2-Mat. 15.957" repete o número anterior; nenhuma fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -21329,14 +21329,14 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Parte (Concessionário Otávio Patrocínio Julião Filho) da concessão de 14/09/2011, renumerada de R-2 para R-3.</t>
+          <t>Parte (Concedente Severino Adilson da Costa) da concessão de 14/09/2011, renumerada de R-2 para R-3.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -21346,39 +21346,39 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>TEXTO</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Retificação e Ratificação, datada de 25 de novembro de 2010, lavrada nestas notas, às fls. 14 a 15, do Livro nº 178, pelo Tabelião [Renato Cordeiro de Arruda], o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o nº 10.091.569/0001-63, com sede na Av. Padre Zuzinha, nº 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Luiz Aragão, nº 63, nesta Cidade, portador do CPF/MF sob o nº 363.437.224-91 e da Cédula de Identidade nº 2.662.495-SSP/PE, concedeu aos Concessionários [Sebastião Estevam], digo, [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da Comunhão Universal de bens, comerciantes, residentes à Rua Manoel João da Silva, nº 70, Cruz Alta, nesta Cidade, portadores dos CPF/MF sob os nºs 206.576.091-53 e 522.283.555-34 e das Cédulas de Identidade nºs 274.843-SSP/MT e 3.445.402-SSP/PE, respectivamente, o direito real de uso do polo nº 443, no setor nº 03, na Rua nº 05, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na Escritura lavrada em 08 de Junho de 2005, no Livro nº 136, às fls. 89v/90v, que era Superfície de Área. Santa Cruz do Capibaribe-PE; 06 de Julho de 2011. Eu, [Rúbrica] O Oficial do Registro. R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 08 de Julho de 2011, Por Escritura, digo, lavrada nestas notas, às fls nº 93 a 93v, do Livro nº 183, o Concedente [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da comunhão universal de bens, comerciantes, residentes nesta Cidade, inscritos nos CPF/MF sob o nos 206.576.091-53 e 522.283.555-34 e portadores das cédulas de Identidade nos 274.843-SSP/MT e 3.445.402-SSP/PE, concedeu aos Srs [José Erivaldo de Almeida] e sua esposa [Ediânia Maria Leite Florêncio de Almeida], brasileiros, casados, comerciantes, gerentes comercial, residentes nesta Cidade, inscrito nos CPF/MF sob o nº 30.201.279-4 SSP/SP e 1.669.311-SSP/PB, o direito real de uso do solo de nº 443, no Setor nº 03, na Rua 05, no Santa Cruz Moda Center, nesta Cidade, para fins comercial, a título gratuito. Santa Cruz do Capibaribe-PE; 02 de Agosto de 2011. Eu, [Rúbrica] A Oficiala do Registro.</t>
+          <t>R-2</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Retificação e Ratificação, datada de 25 de novembro de 2010, lavrada nestas notas, às fls. 14 a 15, do Livro nº 178, pelo Tabelião [Renato Cordeiro de Arruda], o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o nº 10.091.569/0001-63, com sede na Av. Padre Zuzinha, nº 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Luiz Aragão, nº 63, nesta Cidade, portador do CPF/MF sob o nº 363.437.224-91 e da Cédula de Identidade nº 2.662.495-SSP/PE, concedeu aos Concessionários [Sebastião Estevam], digo, [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da Comunhão Universal de bens, comerciantes, residentes à Rua Manoel João da Silva, nº 70, Cruz Alta, nesta Cidade, portadores dos CPF/MF sob os nºs 206.576.091-53 e 522.283.555-34 e das Cédulas de Identidade nºs 274.843-SSP/MT e 3.445.402-SSP/PE, respectivamente, o direito real de uso do polo nº 443, no setor nº 03, na Rua nº 05, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na Escritura lavrada em 08 de Junho de 2005, no Livro nº 136, às fls. 89v/90v, que era Superfície de Área. Santa Cruz do Capibaribe-PE; 06 de Julho de 2011. Eu, [Rúbrica] O Oficial do Registro.</t>
+          <t>R-3</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>O TEXTO desta linha e o da linha 1625 eram iguais e juntavam dois registros: a Retificação e Ratificação (Município concede a Sebastião Barbosa Estevam e Severina Olinda Estevam o direito real de uso do polo 443; assinada em 06 de Julho de 2011) e a Concessão de Direito Real de Uso (Sebastião e Severina concedem a José Erivaldo de Almeida e Ediânia; assinada em 02 de Agosto de 2011). Esta linha (RETIFICAÇÃO E RATIFICAÇÃO, DATA 06/07/2011) ficou só com o trecho da retificação, sem alterar nenhuma palavra.</t>
+          <t>Parte (Concedente Adeilza Maria Costa) da concessão de 14/09/2011, renumerada de R-2 para R-3.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -21388,32 +21388,32 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>TEXTO</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Retificação e Ratificação, datada de 25 de novembro de 2010, lavrada nestas notas, às fls. 14 a 15, do Livro nº 178, pelo Tabelião [Renato Cordeiro de Arruda], o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o nº 10.091.569/0001-63, com sede na Av. Padre Zuzinha, nº 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Luiz Aragão, nº 63, nesta Cidade, portador do CPF/MF sob o nº 363.437.224-91 e da Cédula de Identidade nº 2.662.495-SSP/PE, concedeu aos Concessionários [Sebastião Estevam], digo, [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da Comunhão Universal de bens, comerciantes, residentes à Rua Manoel João da Silva, nº 70, Cruz Alta, nesta Cidade, portadores dos CPF/MF sob os nºs 206.576.091-53 e 522.283.555-34 e das Cédulas de Identidade nºs 274.843-SSP/MT e 3.445.402-SSP/PE, respectivamente, o direito real de uso do polo nº 443, no setor nº 03, na Rua nº 05, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na Escritura lavrada em 08 de Junho de 2005, no Livro nº 136, às fls. 89v/90v, que era Superfície de Área. Santa Cruz do Capibaribe-PE; 06 de Julho de 2011. Eu, [Rúbrica] O Oficial do Registro. R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 08 de Julho de 2011, Por Escritura, digo, lavrada nestas notas, às fls nº 93 a 93v, do Livro nº 183, o Concedente [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da comunhão universal de bens, comerciantes, residentes nesta Cidade, inscritos nos CPF/MF sob o nos 206.576.091-53 e 522.283.555-34 e portadores das cédulas de Identidade nos 274.843-SSP/MT e 3.445.402-SSP/PE, concedeu aos Srs [José Erivaldo de Almeida] e sua esposa [Ediânia Maria Leite Florêncio de Almeida], brasileiros, casados, comerciantes, gerentes comercial, residentes nesta Cidade, inscrito nos CPF/MF sob o nº 30.201.279-4 SSP/SP e 1.669.311-SSP/PB, o direito real de uso do solo de nº 443, no Setor nº 03, na Rua 05, no Santa Cruz Moda Center, nesta Cidade, para fins comercial, a título gratuito. Santa Cruz do Capibaribe-PE; 02 de Agosto de 2011. Eu, [Rúbrica] A Oficiala do Registro.</t>
+          <t>R-2</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 08 de Julho de 2011, Por Escritura, digo, lavrada nestas notas, às fls nº 93 a 93v, do Livro nº 183, o Concedente [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da comunhão universal de bens, comerciantes, residentes nesta Cidade, inscritos nos CPF/MF sob o nos 206.576.091-53 e 522.283.555-34 e portadores das cédulas de Identidade nos 274.843-SSP/MT e 3.445.402-SSP/PE, concedeu aos Srs [José Erivaldo de Almeida] e sua esposa [Ediânia Maria Leite Florêncio de Almeida], brasileiros, casados, comerciantes, gerentes comercial, residentes nesta Cidade, inscrito nos CPF/MF sob o nº 30.201.279-4 SSP/SP e 1.669.311-SSP/PB, o direito real de uso do solo de nº 443, no Setor nº 03, na Rua 05, no Santa Cruz Moda Center, nesta Cidade, para fins comercial, a título gratuito. Santa Cruz do Capibaribe-PE; 02 de Agosto de 2011. Eu, [Rúbrica] A Oficiala do Registro.</t>
+          <t>R-3</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Mesma junção de dois registros da linha 1624. Esta linha (CONCESSÃO DE DIREITO REAL DE USO, DATA 02/08/2011) ficou só com o trecho da concessão a José Erivaldo de Almeida e Ediânia Maria Leite Florêncio de Almeida, sem alterar nenhuma palavra.</t>
+          <t>Parte (Concessionário Otávio Patrocínio Julião Filho) da concessão de 14/09/2011, renumerada de R-2 para R-3.</t>
         </is>
       </c>
     </row>
@@ -21435,27 +21435,27 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>ORDEM</t>
+          <t>TEXTO</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Retificação e Ratificação, datada de 25 de novembro de 2010, lavrada nestas notas, às fls. 14 a 15, do Livro nº 178, pelo Tabelião [Renato Cordeiro de Arruda], o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o nº 10.091.569/0001-63, com sede na Av. Padre Zuzinha, nº 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Luiz Aragão, nº 63, nesta Cidade, portador do CPF/MF sob o nº 363.437.224-91 e da Cédula de Identidade nº 2.662.495-SSP/PE, concedeu aos Concessionários [Sebastião Estevam], digo, [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da Comunhão Universal de bens, comerciantes, residentes à Rua Manoel João da Silva, nº 70, Cruz Alta, nesta Cidade, portadores dos CPF/MF sob os nºs 206.576.091-53 e 522.283.555-34 e das Cédulas de Identidade nºs 274.843-SSP/MT e 3.445.402-SSP/PE, respectivamente, o direito real de uso do polo nº 443, no setor nº 03, na Rua nº 05, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na Escritura lavrada em 08 de Junho de 2005, no Livro nº 136, às fls. 89v/90v, que era Superfície de Área. Santa Cruz do Capibaribe-PE; 06 de Julho de 2011. Eu, [Rúbrica] O Oficial do Registro. R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 08 de Julho de 2011, Por Escritura, digo, lavrada nestas notas, às fls nº 93 a 93v, do Livro nº 183, o Concedente [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da comunhão universal de bens, comerciantes, residentes nesta Cidade, inscritos nos CPF/MF sob o nos 206.576.091-53 e 522.283.555-34 e portadores das cédulas de Identidade nos 274.843-SSP/MT e 3.445.402-SSP/PE, concedeu aos Srs [José Erivaldo de Almeida] e sua esposa [Ediânia Maria Leite Florêncio de Almeida], brasileiros, casados, comerciantes, gerentes comercial, residentes nesta Cidade, inscrito nos CPF/MF sob o nº 30.201.279-4 SSP/SP e 1.669.311-SSP/PB, o direito real de uso do solo de nº 443, no Setor nº 03, na Rua 05, no Santa Cruz Moda Center, nesta Cidade, para fins comercial, a título gratuito. Santa Cruz do Capibaribe-PE; 02 de Agosto de 2011. Eu, [Rúbrica] A Oficiala do Registro.</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Retificação e Ratificação, datada de 25 de novembro de 2010, lavrada nestas notas, às fls. 14 a 15, do Livro nº 178, pelo Tabelião [Renato Cordeiro de Arruda], o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o nº 10.091.569/0001-63, com sede na Av. Padre Zuzinha, nº 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Luiz Aragão, nº 63, nesta Cidade, portador do CPF/MF sob o nº 363.437.224-91 e da Cédula de Identidade nº 2.662.495-SSP/PE, concedeu aos Concessionários [Sebastião Estevam], digo, [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da Comunhão Universal de bens, comerciantes, residentes à Rua Manoel João da Silva, nº 70, Cruz Alta, nesta Cidade, portadores dos CPF/MF sob os nºs 206.576.091-53 e 522.283.555-34 e das Cédulas de Identidade nºs 274.843-SSP/MT e 3.445.402-SSP/PE, respectivamente, o direito real de uso do polo nº 443, no setor nº 03, na Rua nº 05, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na Escritura lavrada em 08 de Junho de 2005, no Livro nº 136, às fls. 89v/90v, que era Superfície de Área. Santa Cruz do Capibaribe-PE; 06 de Julho de 2011. Eu, [Rúbrica] O Oficial do Registro.</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Concessão de Direito Real de Uso de 02/08/2011 (Sebastião Barbosa Estevam e Severina Olinda Estevam a José Erivaldo de Almeida e Ediânia Maria Leite Florêncio de Almeida). Ela pressupõe o R-2 de 06/07/2011, que deu aos concedentes o direito real de uso do polo. Na numeração única R/AV, depois da AV-1 e do R-2 (ambos de 06/07/2011), ela é o 3º ato. O cabeçalho transcrito "R-2 Mat. 16.017" repete o número anterior; nenhuma fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
+          <t>O TEXTO desta linha e o da linha 1625 eram iguais e juntavam dois registros: a Retificação e Ratificação (Município concede a Sebastião Barbosa Estevam e Severina Olinda Estevam o direito real de uso do polo 443; assinada em 06 de Julho de 2011) e a Concessão de Direito Real de Uso (Sebastião e Severina concedem a José Erivaldo de Almeida e Ediânia; assinada em 02 de Agosto de 2011). Esta linha (RETIFICAÇÃO E RATIFICAÇÃO, DATA 06/07/2011) ficou só com o trecho da retificação, sem alterar nenhuma palavra.</t>
         </is>
       </c>
     </row>
@@ -21472,32 +21472,32 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>TEXTO</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>R-2</t>
+          <t>R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Retificação e Ratificação, datada de 25 de novembro de 2010, lavrada nestas notas, às fls. 14 a 15, do Livro nº 178, pelo Tabelião [Renato Cordeiro de Arruda], o outorgante Concedente o [Município de Santa Cruz do Capibaribe-PE], pessoa Jurídica de Direito Público, inscrito no CNPJ/MF sob o nº 10.091.569/0001-63, com sede na Av. Padre Zuzinha, nº 178, Centro, nesta Cidade, neste ato, representado pelo Senhor Prefeito [Antônio Figueirôa de Siqueira], brasileiro, casado, comerciante, residente à Rua Rogaciano Luiz Aragão, nº 63, nesta Cidade, portador do CPF/MF sob o nº 363.437.224-91 e da Cédula de Identidade nº 2.662.495-SSP/PE, concedeu aos Concessionários [Sebastião Estevam], digo, [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da Comunhão Universal de bens, comerciantes, residentes à Rua Manoel João da Silva, nº 70, Cruz Alta, nesta Cidade, portadores dos CPF/MF sob os nºs 206.576.091-53 e 522.283.555-34 e das Cédulas de Identidade nºs 274.843-SSP/MT e 3.445.402-SSP/PE, respectivamente, o direito real de uso do polo nº 443, no setor nº 03, na Rua nº 05, no Santa Cruz Moda Center, nesta Cidade, ficando retificado e ratificado na Escritura lavrada em 08 de Junho de 2005, no Livro nº 136, às fls. 89v/90v, que era Superfície de Área. Santa Cruz do Capibaribe-PE; 06 de Julho de 2011. Eu, [Rúbrica] O Oficial do Registro. R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 08 de Julho de 2011, Por Escritura, digo, lavrada nestas notas, às fls nº 93 a 93v, do Livro nº 183, o Concedente [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da comunhão universal de bens, comerciantes, residentes nesta Cidade, inscritos nos CPF/MF sob o nos 206.576.091-53 e 522.283.555-34 e portadores das cédulas de Identidade nos 274.843-SSP/MT e 3.445.402-SSP/PE, concedeu aos Srs [José Erivaldo de Almeida] e sua esposa [Ediânia Maria Leite Florêncio de Almeida], brasileiros, casados, comerciantes, gerentes comercial, residentes nesta Cidade, inscrito nos CPF/MF sob o nº 30.201.279-4 SSP/SP e 1.669.311-SSP/PB, o direito real de uso do solo de nº 443, no Setor nº 03, na Rua 05, no Santa Cruz Moda Center, nesta Cidade, para fins comercial, a título gratuito. Santa Cruz do Capibaribe-PE; 02 de Agosto de 2011. Eu, [Rúbrica] A Oficiala do Registro.</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>R-3</t>
+          <t>R-2-16017 R-2 Mat. 16.017 Por Escritura Pública de Concessão de Direito Real de Uso, datada de 08 de Julho de 2011, Por Escritura, digo, lavrada nestas notas, às fls nº 93 a 93v, do Livro nº 183, o Concedente [Sebastião Barbosa Estevam] e sua esposa [Severina Olinda Estevam], brasileiros, casados sob o regime da comunhão universal de bens, comerciantes, residentes nesta Cidade, inscritos nos CPF/MF sob o nos 206.576.091-53 e 522.283.555-34 e portadores das cédulas de Identidade nos 274.843-SSP/MT e 3.445.402-SSP/PE, concedeu aos Srs [José Erivaldo de Almeida] e sua esposa [Ediânia Maria Leite Florêncio de Almeida], brasileiros, casados, comerciantes, gerentes comercial, residentes nesta Cidade, inscrito nos CPF/MF sob o nº 30.201.279-4 SSP/SP e 1.669.311-SSP/PB, o direito real de uso do solo de nº 443, no Setor nº 03, na Rua 05, no Santa Cruz Moda Center, nesta Cidade, para fins comercial, a título gratuito. Santa Cruz do Capibaribe-PE; 02 de Agosto de 2011. Eu, [Rúbrica] A Oficiala do Registro.</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Parte (Concedente Sebastião Barbosa Estevam) da Concessão de Direito Real de Uso de 02/08/2011, renumerada de R-2 para R-3.</t>
+          <t>Mesma junção de dois registros da linha 1624. Esta linha (CONCESSÃO DE DIREITO REAL DE USO, DATA 02/08/2011) ficou só com o trecho da concessão a José Erivaldo de Almeida e Ediânia Maria Leite Florêncio de Almeida, sem alterar nenhuma palavra.</t>
         </is>
       </c>
     </row>
@@ -21514,32 +21514,32 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ORDEM</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>R-2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>R-3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Parte (Concedente Severina Olinda Estevam) da Concessão de Direito Real de Uso de 02/08/2011, renumerada de R-2 para R-3.</t>
+          <t>Concessão de Direito Real de Uso de 02/08/2011 (Sebastião Barbosa Estevam e Severina Olinda Estevam a José Erivaldo de Almeida e Ediânia Maria Leite Florêncio de Almeida). Ela pressupõe o R-2 de 06/07/2011, que deu aos concedentes o direito real de uso do polo. Na numeração única R/AV, depois da AV-1 e do R-2 (ambos de 06/07/2011), ela é o 3º ato. O cabeçalho transcrito "R-2 Mat. 16.017" repete o número anterior; nenhuma fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
         </is>
       </c>
     </row>
@@ -21561,7 +21561,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -21581,7 +21581,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Parte (Concessionário José Erivaldo de Almeida) da Concessão de Direito Real de Uso de 02/08/2011, renumerada de R-2 para R-3.</t>
+          <t>Parte (Concedente Sebastião Barbosa Estevam) da Concessão de Direito Real de Uso de 02/08/2011, renumerada de R-2 para R-3.</t>
         </is>
       </c>
     </row>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -21623,14 +21623,14 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Parte (Concessionária Ediânia Maria Leite Florêncio de Almeida) da Concessão de Direito Real de Uso de 02/08/2011, renumerada de R-2 para R-3.</t>
+          <t>Parte (Concedente Severina Olinda Estevam) da Concessão de Direito Real de Uso de 02/08/2011, renumerada de R-2 para R-3.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -21640,39 +21640,39 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>ORDEM</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>R-2</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>R-3</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Compra e venda de 05/11/2012 (José Francisco da Silva Leão e Gercina Ursulino de Souza Leão a Ernando Corado de Souza). O número 3 já é da AV-3 (certidão de averbação da construção, 07/03/2012), cujo texto começa com "Av.3". Os três atos de 07/03/2012 têm cabeçalhos "R.1", "Av.2" e "Av.3", o que mostra que nesta matrícula R e AV seguem uma numeração única; esta venda é o primeiro ato depois deles, portanto o 4º. O cabeçalho transcrito "R.3" repete o número da AV-3; nenhuma outra fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
+          <t>Parte (Concessionário José Erivaldo de Almeida) da Concessão de Direito Real de Uso de 02/08/2011, renumerada de R-2 para R-3.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -21687,7 +21687,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -21697,17 +21697,17 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
+          <t>R-2</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
           <t>R-3</t>
         </is>
       </c>
-      <c r="G475" t="inlineStr">
-        <is>
-          <t>R-4</t>
-        </is>
-      </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Parte (Transmitente José Francisco da Silva Leão) da compra e venda de 05/11/2012, renumerada de R-3 para R-4.</t>
+          <t>Parte (Concessionária Ediânia Maria Leite Florêncio de Almeida) da Concessão de Direito Real de Uso de 02/08/2011, renumerada de R-2 para R-3.</t>
         </is>
       </c>
     </row>
@@ -21724,32 +21724,32 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ORDEM</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>R-3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>R-4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Parte (Transmitente Gercina Ursulino de Souza Leão) da compra e venda de 05/11/2012, renumerada de R-3 para R-4.</t>
+          <t>Compra e venda de 05/11/2012 (José Francisco da Silva Leão e Gercina Ursulino de Souza Leão a Ernando Corado de Souza). O número 3 já é da AV-3 (certidão de averbação da construção, 07/03/2012), cujo texto começa com "Av.3". Os três atos de 07/03/2012 têm cabeçalhos "R.1", "Av.2" e "Av.3", o que mostra que nesta matrícula R e AV seguem uma numeração única; esta venda é o primeiro ato depois deles, portanto o 4º. O cabeçalho transcrito "R.3" repete o número da AV-3; nenhuma outra fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
         </is>
       </c>
     </row>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -21791,14 +21791,14 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Parte (Adquirente Ernando Corado de Souza) da compra e venda de 05/11/2012, renumerada de R-3 para R-4.</t>
+          <t>Parte (Transmitente José Francisco da Silva Leão) da compra e venda de 05/11/2012, renumerada de R-3 para R-4.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>16887</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -21808,69 +21808,81 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>ORDEM</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>R-3</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>R-4</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Averbação de 23/11/2012: certidão de que o lote nº 18 ganhou a matrícula nº 17.899 (livro 2-EA, fls. 83). O número 3 já é da averbação de 25/04/2012 (lote 18-A aberto sob a matrícula nº 17.026). Na numeração única R/AV, depois de R-1 e AV-2 (21/03/2012) e da AV-3 (25/04/2012), ela é o 4º ato. O cabeçalho transcrito "AV.3 MAT 16925" repete o número anterior; nenhuma fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
+          <t>Parte (Transmitente Gercina Ursulino de Souza Leão) da compra e venda de 05/11/2012, renumerada de R-3 para R-4.</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>16887</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>linha retirada</t>
+          <t>alteração</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>MATRICULA_ATO</t>
+          <t>ATO_PARTES</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>2635</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
-      <c r="G479" t="inlineStr"/>
+          <t>4939</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>R-3</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>R-4</t>
+        </is>
+      </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>AV-2 de 23/08/2013 (desmembramento do lote 20 em 20, 20-A e 20-B) anulada no próprio livro: o texto termina com "NOTA: Certifico e dou fé, que fica cancelado o AV 2 da presente matrícula, em virtude do desmembramento só poder ser feito após o remembramento dos lotes 20 e 22 da quadra A7, loteamento Santa Filomena", no mesmo dia. O número AV-2 foi reaproveitado para o remembramento de 13/09/2013 (linha 2636). Não tinha partes ligadas.</t>
+          <t>Parte (Adquirente Ernando Corado de Souza) da compra e venda de 05/11/2012, renumerada de R-3 para R-4.</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -21885,7 +21897,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -21895,29 +21907,29 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Averbação da construção (certidão de averbação, 11/12/2012), lançada logo depois do Habite-se do mesmo dia. A matrícula segue a numeração única R/AV: depois dela vêm "AV.4-17.506" (02/06/2016), "R.5-17.506" e "R.6-17.506" (10/01/2017), o que mostra que os números 2 e 3 foram usados pelas duas averbações de 11/12/2012, já que o 1 é o R-1 (20/08/2012). O cabeçalho transcrito "AV. 2" seguia a contagem só das averbações; pela sequência do livro ela é a AV-3.</t>
+          <t>Averbação de 23/11/2012: certidão de que o lote nº 18 ganhou a matrícula nº 17.899 (livro 2-EA, fls. 83). O número 3 já é da averbação de 25/04/2012 (lote 18-A aberto sob a matrícula nº 17.026). Na numeração única R/AV, depois de R-1 e AV-2 (21/03/2012) e da AV-3 (25/04/2012), ela é o 4º ato. O cabeçalho transcrito "AV.3 MAT 16925" repete o número anterior; nenhuma fonte traz outra numeração, por isso a correção segue a ordem cronológica.</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>alteração</t>
+          <t>linha retirada</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -21927,27 +21939,15 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>3109</t>
-        </is>
-      </c>
-      <c r="E481" t="inlineStr">
-        <is>
-          <t>ORDEM</t>
-        </is>
-      </c>
-      <c r="F481" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G481" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>2635</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Averbação do Habite-se (11/12/2012), primeiro ato depois do R-1 (compra e venda de 20/08/2012), que já ocupa o número 1. Como os atos seguintes são AV.4, R.5 e R.6, os números 2 e 3 são das duas averbações de 11/12/2012, e o Habite-se é a primeira delas. O cabeçalho transcrito "AV. 1" seguia a contagem só das averbações; pela sequência do livro ela é a AV-2.</t>
+          <t>AV-2 de 23/08/2013 (desmembramento do lote 20 em 20, 20-A e 20-B) anulada no próprio livro: o texto termina com "NOTA: Certifico e dou fé, que fica cancelado o AV 2 da presente matrícula, em virtude do desmembramento só poder ser feito após o remembramento dos lotes 20 e 22 da quadra A7, loteamento Santa Filomena", no mesmo dia. O número AV-2 foi reaproveitado para o remembramento de 13/09/2013 (linha 2636). Não tinha partes ligadas.</t>
         </is>
       </c>
     </row>
@@ -21964,32 +21964,32 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ORDEM</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>AV-2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>AV-3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Parte (PROPRIETÁRIO Lucilene Maria da Silva) da averbação da construção de 11/12/2012, renumerada de AV-2 para AV-3.</t>
+          <t>Averbação da construção (certidão de averbação, 11/12/2012), lançada logo depois do Habite-se do mesmo dia. A matrícula segue a numeração única R/AV: depois dela vêm "AV.4-17.506" (02/06/2016), "R.5-17.506" e "R.6-17.506" (10/01/2017), o que mostra que os números 2 e 3 foram usados pelas duas averbações de 11/12/2012, já que o 1 é o R-1 (20/08/2012). O cabeçalho transcrito "AV. 2" seguia a contagem só das averbações; pela sequência do livro ela é a AV-3.</t>
         </is>
       </c>
     </row>
@@ -22006,30 +22006,114 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>ATO_PARTES</t>
+          <t>MATRICULA_ATO</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>ORDEM</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Averbação do Habite-se (11/12/2012), primeiro ato depois do R-1 (compra e venda de 20/08/2012), que já ocupa o número 1. Como os atos seguintes são AV.4, R.5 e R.6, os números 2 e 3 são das duas averbações de 11/12/2012, e o Habite-se é a primeira delas. O cabeçalho transcrito "AV. 1" seguia a contagem só das averbações; pela sequência do livro ela é a AV-2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>17506</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>alteração</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>ATO_PARTES</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>AV-2</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>AV-3</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Parte (PROPRIETÁRIO Lucilene Maria da Silva) da averbação da construção de 11/12/2012, renumerada de AV-2 para AV-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>17506</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>alteração</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>ATO_PARTES</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
           <t>6200</t>
         </is>
       </c>
-      <c r="E483" t="inlineStr">
+      <c r="E485" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr">
+      <c r="F485" t="inlineStr">
         <is>
           <t>AV-1</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr">
+      <c r="G485" t="inlineStr">
         <is>
           <t>AV-2</t>
         </is>
       </c>
-      <c r="H483" t="inlineStr">
+      <c r="H485" t="inlineStr">
         <is>
           <t>Parte (PROPRIETÁRIO Lucilene Maria da Silva) da averbação do Habite-se de 11/12/2012, renumerada de AV-1 para AV-2.</t>
         </is>
